--- a/04_Figures/F06_prediction/modules/total/ridge/c_data/results.xlsx
+++ b/04_Figures/F06_prediction/modules/total/ridge/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -168,12 +168,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -566,16 +560,16 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.193117677048927</v>
       </c>
       <c r="I2" t="n">
-        <v>-1</v>
+        <v>-0.973626373626374</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -599,28 +593,28 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
         <v>200</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.193117677048927</v>
       </c>
       <c r="I3" t="n">
-        <v>-1</v>
+        <v>-0.973626373626374</v>
       </c>
       <c r="J3" t="n">
-        <v>0.203980099502488</v>
+        <v>0.761194029850746</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0.288557213930348</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.15904255716776</v>
+        <v>-0.187199701105735</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0250725552051114</v>
+        <v>0.133252574131291</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +634,7 @@
         <v>14</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -673,7 +667,7 @@
         <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
         <v>200</v>
@@ -685,16 +679,16 @@
         <v>-1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.930348258706468</v>
+        <v>0.587064676616915</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.159989245224142</v>
+        <v>-0.219039106686836</v>
       </c>
       <c r="M5" t="n">
-        <v>0.00596226905143458</v>
+        <v>0.143433172522863</v>
       </c>
     </row>
     <row r="6">
@@ -714,16 +708,16 @@
         <v>14</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.340375090105546</v>
       </c>
       <c r="I6" t="n">
-        <v>-1</v>
+        <v>-0.956043956043956</v>
       </c>
       <c r="J6"/>
       <c r="K6"/>
@@ -747,28 +741,28 @@
         <v>14</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
         <v>200</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.340375090105546</v>
       </c>
       <c r="I7" t="n">
-        <v>-1</v>
+        <v>-0.956043956043956</v>
       </c>
       <c r="J7" t="n">
-        <v>0.477611940298507</v>
+        <v>0.870646766169154</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0.189054726368159</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.160169475745852</v>
+        <v>-0.216048284889458</v>
       </c>
       <c r="M7" t="n">
-        <v>0.00225529447023013</v>
+        <v>0.152214757665769</v>
       </c>
     </row>
     <row r="8">
@@ -788,16 +782,16 @@
         <v>14</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.0908985192850358</v>
       </c>
       <c r="I8" t="n">
-        <v>-1</v>
+        <v>-0.485714285714286</v>
       </c>
       <c r="J8"/>
       <c r="K8"/>
@@ -821,28 +815,28 @@
         <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
         <v>200</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.0908985192850358</v>
       </c>
       <c r="I9" t="n">
-        <v>-1</v>
+        <v>-0.485714285714286</v>
       </c>
       <c r="J9" t="n">
-        <v>0.562189054726368</v>
+        <v>0.0398009950248756</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0.0597014925373134</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.159838350944893</v>
+        <v>-0.19111716569569</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00114837272836856</v>
+        <v>0.113941631222515</v>
       </c>
     </row>
     <row r="10">
@@ -862,7 +856,7 @@
         <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -895,7 +889,7 @@
         <v>14</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
         <v>200</v>
@@ -907,16 +901,16 @@
         <v>-0.996690559042565</v>
       </c>
       <c r="J11" t="n">
-        <v>0.791044776119403</v>
+        <v>0.527363184079602</v>
       </c>
       <c r="K11" t="n">
-        <v>0.522388059701492</v>
+        <v>0.701492537313433</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.160364123911595</v>
+        <v>-0.183817075845556</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0158977720329979</v>
+        <v>0.152111357348666</v>
       </c>
     </row>
     <row r="12">
@@ -936,16 +930,16 @@
         <v>13</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.533361078761485</v>
       </c>
       <c r="I12" t="n">
-        <v>-1</v>
+        <v>-0.801104972375691</v>
       </c>
       <c r="J12"/>
       <c r="K12"/>
@@ -969,28 +963,28 @@
         <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
         <v>200</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.533361078761485</v>
       </c>
       <c r="I13" t="n">
-        <v>-1</v>
+        <v>-0.801104972375691</v>
       </c>
       <c r="J13" t="n">
-        <v>0.398009950248756</v>
+        <v>0.955223880597015</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0.129353233830846</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.173715323789809</v>
+        <v>-0.22099089857534</v>
       </c>
       <c r="M13" t="n">
-        <v>0.00256219401811369</v>
+        <v>0.159231386662201</v>
       </c>
     </row>
   </sheetData>
@@ -1045,7 +1039,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.290903176961868</v>
       </c>
     </row>
     <row r="5">
@@ -1078,7 +1072,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.165345894503802</v>
+        <v>-0.0431358529729442</v>
       </c>
     </row>
     <row r="8">
@@ -1089,7 +1083,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.17932853423175</v>
       </c>
     </row>
     <row r="9">
@@ -1122,7 +1116,7 @@
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.229756290029264</v>
       </c>
     </row>
     <row r="12">
@@ -1155,7 +1149,7 @@
         <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.196116008097952</v>
       </c>
     </row>
     <row r="15">
@@ -1199,7 +1193,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.175893693498824</v>
+        <v>-0.573221060298079</v>
       </c>
     </row>
     <row r="19">
@@ -1320,7 +1314,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.0671642481814936</v>
       </c>
     </row>
     <row r="30">
@@ -1331,7 +1325,7 @@
         <v>16</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.305779762526488</v>
       </c>
     </row>
     <row r="31">
@@ -1353,7 +1347,7 @@
         <v>16</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.289141196485176</v>
       </c>
     </row>
     <row r="33">
@@ -1375,7 +1369,7 @@
         <v>16</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.174912224035193</v>
       </c>
     </row>
     <row r="35">
@@ -1386,7 +1380,7 @@
         <v>16</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.165981050134774</v>
+        <v>-0.315925361304432</v>
       </c>
     </row>
     <row r="36">
@@ -1397,7 +1391,7 @@
         <v>16</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.176644977694286</v>
+        <v>-0.238040637639709</v>
       </c>
     </row>
     <row r="37">
@@ -1419,7 +1413,7 @@
         <v>16</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.17448693649849</v>
+        <v>-0.184266536765105</v>
       </c>
     </row>
     <row r="39">
@@ -1430,7 +1424,7 @@
         <v>16</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.192580541703069</v>
       </c>
     </row>
     <row r="40">
@@ -1485,7 +1479,7 @@
         <v>16</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.339295052664355</v>
       </c>
     </row>
     <row r="45">
@@ -1540,7 +1534,7 @@
         <v>16</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.167781316298914</v>
+        <v>-0.229463460329839</v>
       </c>
     </row>
     <row r="50">
@@ -1562,7 +1556,7 @@
         <v>16</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.351176214335165</v>
       </c>
     </row>
     <row r="52">
@@ -1584,7 +1578,7 @@
         <v>16</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.51980150381794</v>
       </c>
     </row>
     <row r="54">
@@ -1595,7 +1589,7 @@
         <v>16</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.507747482583193</v>
       </c>
     </row>
     <row r="55">
@@ -1606,7 +1600,7 @@
         <v>16</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.16980069473174</v>
+        <v>-0.201639037359092</v>
       </c>
     </row>
     <row r="56">
@@ -1617,7 +1611,7 @@
         <v>16</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.278022052083175</v>
       </c>
     </row>
     <row r="57">
@@ -1639,7 +1633,7 @@
         <v>16</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.318230078779643</v>
       </c>
     </row>
     <row r="59">
@@ -1672,7 +1666,7 @@
         <v>16</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.348450117760384</v>
       </c>
     </row>
     <row r="62">
@@ -1705,7 +1699,7 @@
         <v>16</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.19544518825222</v>
+        <v>-0.272931570939561</v>
       </c>
     </row>
     <row r="65">
@@ -1727,7 +1721,7 @@
         <v>16</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.361516286635671</v>
       </c>
     </row>
     <row r="67">
@@ -1749,7 +1743,7 @@
         <v>16</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.508033336890796</v>
       </c>
     </row>
     <row r="69">
@@ -1782,7 +1776,7 @@
         <v>16</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.177681376950612</v>
       </c>
     </row>
     <row r="72">
@@ -1826,7 +1820,7 @@
         <v>16</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.289176864223761</v>
       </c>
     </row>
     <row r="76">
@@ -1837,7 +1831,7 @@
         <v>16</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.135061015828066</v>
       </c>
     </row>
     <row r="77">
@@ -1881,7 +1875,7 @@
         <v>16</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.438288560266866</v>
       </c>
     </row>
     <row r="81">
@@ -1936,7 +1930,7 @@
         <v>16</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.180933536802168</v>
       </c>
     </row>
     <row r="86">
@@ -1947,7 +1941,7 @@
         <v>16</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.157940818148429</v>
+        <v>-0.0129257159016434</v>
       </c>
     </row>
     <row r="87">
@@ -1958,7 +1952,7 @@
         <v>16</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.157931266080258</v>
       </c>
     </row>
     <row r="88">
@@ -1969,7 +1963,7 @@
         <v>16</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.0152474629261974</v>
       </c>
     </row>
     <row r="89">
@@ -1980,7 +1974,7 @@
         <v>16</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.293165760427413</v>
       </c>
     </row>
     <row r="90">
@@ -2024,7 +2018,7 @@
         <v>16</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.165736652905754</v>
+        <v>-0.279119850184606</v>
       </c>
     </row>
     <row r="94">
@@ -2068,7 +2062,7 @@
         <v>16</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.336481864604341</v>
       </c>
     </row>
     <row r="98">
@@ -2090,7 +2084,7 @@
         <v>16</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.154406968196177</v>
       </c>
     </row>
     <row r="100">
@@ -2101,7 +2095,7 @@
         <v>16</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.061112885361086</v>
       </c>
     </row>
     <row r="101">
@@ -2200,7 +2194,7 @@
         <v>16</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.125727760786678</v>
       </c>
     </row>
     <row r="110">
@@ -2211,7 +2205,7 @@
         <v>16</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.158189677652333</v>
       </c>
     </row>
     <row r="111">
@@ -2233,7 +2227,7 @@
         <v>16</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.228714680917195</v>
       </c>
     </row>
     <row r="113">
@@ -2277,7 +2271,7 @@
         <v>16</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.163103264281383</v>
       </c>
     </row>
     <row r="117">
@@ -2288,7 +2282,7 @@
         <v>16</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.13321322615594</v>
       </c>
     </row>
     <row r="118">
@@ -2310,7 +2304,7 @@
         <v>16</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.171536063243593</v>
       </c>
     </row>
     <row r="120">
@@ -2321,7 +2315,7 @@
         <v>16</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.175412868240118</v>
       </c>
     </row>
     <row r="121">
@@ -2343,7 +2337,7 @@
         <v>16</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.928084293693491</v>
       </c>
     </row>
     <row r="123">
@@ -2354,7 +2348,7 @@
         <v>16</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.168871881461845</v>
+        <v>0.311759687199945</v>
       </c>
     </row>
     <row r="124">
@@ -2365,7 +2359,7 @@
         <v>16</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.176341237902709</v>
+        <v>-0.012935822890769</v>
       </c>
     </row>
     <row r="125">
@@ -2376,7 +2370,7 @@
         <v>16</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.379515859568897</v>
       </c>
     </row>
     <row r="126">
@@ -2409,7 +2403,7 @@
         <v>16</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.285031174544113</v>
       </c>
     </row>
     <row r="129">
@@ -2420,7 +2414,7 @@
         <v>16</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.404339222061207</v>
       </c>
     </row>
     <row r="130">
@@ -2453,7 +2447,7 @@
         <v>16</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.877264813752327</v>
       </c>
     </row>
     <row r="133">
@@ -2464,7 +2458,7 @@
         <v>16</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.173833346023467</v>
       </c>
     </row>
     <row r="134">
@@ -2486,7 +2480,7 @@
         <v>16</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.31767279515969</v>
       </c>
     </row>
     <row r="136">
@@ -2519,7 +2513,7 @@
         <v>16</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.315721976885344</v>
       </c>
     </row>
     <row r="139">
@@ -2585,7 +2579,7 @@
         <v>16</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.273737944881256</v>
       </c>
     </row>
     <row r="145">
@@ -2618,7 +2612,7 @@
         <v>16</v>
       </c>
       <c r="C147" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.338393998168442</v>
       </c>
     </row>
     <row r="148">
@@ -2651,7 +2645,7 @@
         <v>16</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.276517446685048</v>
       </c>
     </row>
     <row r="151">
@@ -2673,7 +2667,7 @@
         <v>16</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.182251271312661</v>
+        <v>-0.199424609655666</v>
       </c>
     </row>
     <row r="153">
@@ -2706,7 +2700,7 @@
         <v>16</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.366611419496302</v>
       </c>
     </row>
     <row r="156">
@@ -2717,7 +2711,7 @@
         <v>16</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.292146361936521</v>
       </c>
     </row>
     <row r="157">
@@ -2761,7 +2755,7 @@
         <v>16</v>
       </c>
       <c r="C160" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.180037481551102</v>
       </c>
     </row>
     <row r="161">
@@ -2783,7 +2777,7 @@
         <v>16</v>
       </c>
       <c r="C162" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.242366086045217</v>
       </c>
     </row>
     <row r="163">
@@ -2794,7 +2788,7 @@
         <v>16</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.182449244731119</v>
       </c>
     </row>
     <row r="164">
@@ -2816,7 +2810,7 @@
         <v>16</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.239313615423247</v>
       </c>
     </row>
     <row r="166">
@@ -2827,7 +2821,7 @@
         <v>16</v>
       </c>
       <c r="C166" t="n">
-        <v>-0.159763313609468</v>
+        <v>0.231216103298203</v>
       </c>
     </row>
     <row r="167">
@@ -2849,7 +2843,7 @@
         <v>16</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.163678803404922</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="169">
@@ -2871,7 +2865,7 @@
         <v>16</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.181144989756462</v>
       </c>
     </row>
     <row r="171">
@@ -2904,7 +2898,7 @@
         <v>16</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.185939905181094</v>
       </c>
     </row>
     <row r="174">
@@ -2915,7 +2909,7 @@
         <v>16</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.213710238978898</v>
       </c>
     </row>
     <row r="175">
@@ -2926,7 +2920,7 @@
         <v>16</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.166994922666003</v>
       </c>
     </row>
     <row r="176">
@@ -2937,7 +2931,7 @@
         <v>16</v>
       </c>
       <c r="C176" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.205810395582239</v>
       </c>
     </row>
     <row r="177">
@@ -2948,7 +2942,7 @@
         <v>16</v>
       </c>
       <c r="C177" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.21746432677902</v>
       </c>
     </row>
     <row r="178">
@@ -2981,7 +2975,7 @@
         <v>16</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.158547769883538</v>
+        <v>-0.14063900096411</v>
       </c>
     </row>
     <row r="181">
@@ -3003,7 +2997,7 @@
         <v>16</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.17173818114993</v>
+        <v>-0.21298576354953</v>
       </c>
     </row>
     <row r="183">
@@ -3047,7 +3041,7 @@
         <v>16</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.178874027601871</v>
+        <v>-0.355647448468949</v>
       </c>
     </row>
     <row r="187">
@@ -3069,7 +3063,7 @@
         <v>16</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.160184249176329</v>
+        <v>-0.390967654451502</v>
       </c>
     </row>
     <row r="189">
@@ -3091,7 +3085,7 @@
         <v>16</v>
       </c>
       <c r="C190" t="n">
-        <v>0.188780363915413</v>
+        <v>0.350314980978878</v>
       </c>
     </row>
     <row r="191">
@@ -3102,7 +3096,7 @@
         <v>16</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.193649166024283</v>
       </c>
     </row>
     <row r="192">
@@ -3113,7 +3107,7 @@
         <v>16</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.312239103539096</v>
       </c>
     </row>
     <row r="193">
@@ -3135,7 +3129,7 @@
         <v>16</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.164350703202164</v>
+        <v>-0.171057935500493</v>
       </c>
     </row>
     <row r="195">
@@ -3201,7 +3195,7 @@
         <v>16</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.269569322761389</v>
       </c>
     </row>
     <row r="201">
@@ -3223,7 +3217,7 @@
         <v>16</v>
       </c>
       <c r="C202" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.925218317059011</v>
       </c>
     </row>
     <row r="203">
@@ -3234,7 +3228,7 @@
         <v>16</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.51822504767232</v>
       </c>
     </row>
     <row r="204">
@@ -3245,7 +3239,7 @@
         <v>16</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.328394432514278</v>
       </c>
     </row>
     <row r="205">
@@ -3278,7 +3272,7 @@
         <v>16</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.179119664306638</v>
       </c>
     </row>
     <row r="208">
@@ -3322,7 +3316,7 @@
         <v>16</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.48730124030518</v>
       </c>
     </row>
     <row r="212">
@@ -3344,7 +3338,7 @@
         <v>16</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.347708223811659</v>
       </c>
     </row>
     <row r="214">
@@ -3355,7 +3349,7 @@
         <v>16</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.414226553524506</v>
       </c>
     </row>
     <row r="215">
@@ -3366,7 +3360,7 @@
         <v>16</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.30340613438503</v>
       </c>
     </row>
     <row r="216">
@@ -3388,7 +3382,7 @@
         <v>16</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.217661450527669</v>
       </c>
     </row>
     <row r="218">
@@ -3509,7 +3503,7 @@
         <v>16</v>
       </c>
       <c r="C228" t="n">
-        <v>-0.162230081538765</v>
+        <v>-0.179252194011534</v>
       </c>
     </row>
     <row r="229">
@@ -3520,7 +3514,7 @@
         <v>16</v>
       </c>
       <c r="C229" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.231171336753283</v>
       </c>
     </row>
     <row r="230">
@@ -3531,7 +3525,7 @@
         <v>16</v>
       </c>
       <c r="C230" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.517519004947218</v>
       </c>
     </row>
     <row r="231">
@@ -3575,7 +3569,7 @@
         <v>16</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.358216661573166</v>
       </c>
     </row>
     <row r="235">
@@ -3586,7 +3580,7 @@
         <v>16</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.171014182700535</v>
+        <v>-0.402433865078603</v>
       </c>
     </row>
     <row r="236">
@@ -3608,7 +3602,7 @@
         <v>16</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.0566061934214597</v>
       </c>
     </row>
     <row r="238">
@@ -3619,7 +3613,7 @@
         <v>16</v>
       </c>
       <c r="C238" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.235403809365907</v>
       </c>
     </row>
     <row r="239">
@@ -3630,7 +3624,7 @@
         <v>16</v>
       </c>
       <c r="C239" t="n">
-        <v>-0.145815308651991</v>
+        <v>0.23254999293915</v>
       </c>
     </row>
     <row r="240">
@@ -3663,7 +3657,7 @@
         <v>16</v>
       </c>
       <c r="C242" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.494398753959993</v>
       </c>
     </row>
     <row r="243">
@@ -3674,7 +3668,7 @@
         <v>16</v>
       </c>
       <c r="C243" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.390046008595171</v>
       </c>
     </row>
     <row r="244">
@@ -3685,7 +3679,7 @@
         <v>16</v>
       </c>
       <c r="C244" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.331175947205936</v>
       </c>
     </row>
     <row r="245">
@@ -3696,7 +3690,7 @@
         <v>16</v>
       </c>
       <c r="C245" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.559119984238979</v>
       </c>
     </row>
     <row r="246">
@@ -3718,7 +3712,7 @@
         <v>16</v>
       </c>
       <c r="C247" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.273282690937448</v>
       </c>
     </row>
     <row r="248">
@@ -3762,7 +3756,7 @@
         <v>16</v>
       </c>
       <c r="C251" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.535714233652478</v>
       </c>
     </row>
     <row r="252">
@@ -3795,7 +3789,7 @@
         <v>16</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.301055198547002</v>
       </c>
     </row>
     <row r="255">
@@ -3806,7 +3800,7 @@
         <v>16</v>
       </c>
       <c r="C255" t="n">
-        <v>-0.164078479533963</v>
+        <v>-0.196486510523128</v>
       </c>
     </row>
     <row r="256">
@@ -3850,7 +3844,7 @@
         <v>16</v>
       </c>
       <c r="C259" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.204860160655147</v>
       </c>
     </row>
     <row r="260">
@@ -3905,7 +3899,7 @@
         <v>16</v>
       </c>
       <c r="C264" t="n">
-        <v>-0.169371655193038</v>
+        <v>-0.252479233098215</v>
       </c>
     </row>
     <row r="265">
@@ -3916,7 +3910,7 @@
         <v>16</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.181396332539324</v>
+        <v>-0.312449143180877</v>
       </c>
     </row>
     <row r="266">
@@ -3938,7 +3932,7 @@
         <v>16</v>
       </c>
       <c r="C267" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.429364441218794</v>
       </c>
     </row>
     <row r="268">
@@ -3949,7 +3943,7 @@
         <v>16</v>
       </c>
       <c r="C268" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.514451299462293</v>
       </c>
     </row>
     <row r="269">
@@ -4037,7 +4031,7 @@
         <v>16</v>
       </c>
       <c r="C276" t="n">
-        <v>-0.172161871338402</v>
+        <v>-0.199132499412937</v>
       </c>
     </row>
     <row r="277">
@@ -4048,7 +4042,7 @@
         <v>16</v>
       </c>
       <c r="C277" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.200923678800891</v>
       </c>
     </row>
     <row r="278">
@@ -4081,7 +4075,7 @@
         <v>16</v>
       </c>
       <c r="C280" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.23120465192881</v>
       </c>
     </row>
     <row r="281">
@@ -4136,7 +4130,7 @@
         <v>16</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.423640645789191</v>
       </c>
     </row>
     <row r="286">
@@ -4147,7 +4141,7 @@
         <v>16</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.179443048453998</v>
       </c>
     </row>
     <row r="287">
@@ -4158,7 +4152,7 @@
         <v>16</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.30548008465781</v>
       </c>
     </row>
     <row r="288">
@@ -4169,7 +4163,7 @@
         <v>16</v>
       </c>
       <c r="C288" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.234667112409488</v>
       </c>
     </row>
     <row r="289">
@@ -4180,7 +4174,7 @@
         <v>16</v>
       </c>
       <c r="C289" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.71219884015717</v>
       </c>
     </row>
     <row r="290">
@@ -4213,7 +4207,7 @@
         <v>16</v>
       </c>
       <c r="C292" t="n">
-        <v>-0.17374707234307</v>
+        <v>-0.182473905408702</v>
       </c>
     </row>
     <row r="293">
@@ -4235,7 +4229,7 @@
         <v>16</v>
       </c>
       <c r="C294" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.239221222562956</v>
       </c>
     </row>
     <row r="295">
@@ -4268,7 +4262,7 @@
         <v>16</v>
       </c>
       <c r="C297" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.189648992226581</v>
       </c>
     </row>
     <row r="298">
@@ -4301,7 +4295,7 @@
         <v>16</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.316239392259831</v>
       </c>
     </row>
     <row r="301">
@@ -4312,7 +4306,7 @@
         <v>16</v>
       </c>
       <c r="C301" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.197223349668059</v>
       </c>
     </row>
     <row r="302">
@@ -4345,7 +4339,7 @@
         <v>16</v>
       </c>
       <c r="C304" t="n">
-        <v>-0.184715478921796</v>
+        <v>-0.230178204523459</v>
       </c>
     </row>
     <row r="305">
@@ -4411,7 +4405,7 @@
         <v>16</v>
       </c>
       <c r="C310" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.18156596119181</v>
       </c>
     </row>
     <row r="311">
@@ -4422,7 +4416,7 @@
         <v>16</v>
       </c>
       <c r="C311" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.322598268136337</v>
       </c>
     </row>
     <row r="312">
@@ -4444,7 +4438,7 @@
         <v>16</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.225781413153003</v>
       </c>
     </row>
     <row r="314">
@@ -4477,7 +4471,7 @@
         <v>16</v>
       </c>
       <c r="C316" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.441951204114176</v>
       </c>
     </row>
     <row r="317">
@@ -4499,7 +4493,7 @@
         <v>16</v>
       </c>
       <c r="C318" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.496683782365029</v>
       </c>
     </row>
     <row r="319">
@@ -4532,7 +4526,7 @@
         <v>16</v>
       </c>
       <c r="C321" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.295520118755906</v>
       </c>
     </row>
     <row r="322">
@@ -4554,7 +4548,7 @@
         <v>16</v>
       </c>
       <c r="C323" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.198520676398226</v>
       </c>
     </row>
     <row r="324">
@@ -4565,7 +4559,7 @@
         <v>16</v>
       </c>
       <c r="C324" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.686832165864056</v>
       </c>
     </row>
     <row r="325">
@@ -4576,7 +4570,7 @@
         <v>16</v>
       </c>
       <c r="C325" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.468029016341744</v>
       </c>
     </row>
     <row r="326">
@@ -4609,7 +4603,7 @@
         <v>16</v>
       </c>
       <c r="C328" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.298225413482967</v>
       </c>
     </row>
     <row r="329">
@@ -4620,7 +4614,7 @@
         <v>16</v>
       </c>
       <c r="C329" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.340977164182876</v>
       </c>
     </row>
     <row r="330">
@@ -4642,7 +4636,7 @@
         <v>16</v>
       </c>
       <c r="C331" t="n">
-        <v>-0.167622236036337</v>
+        <v>-0.48450789763434</v>
       </c>
     </row>
     <row r="332">
@@ -4664,7 +4658,7 @@
         <v>16</v>
       </c>
       <c r="C333" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.178240218759622</v>
       </c>
     </row>
     <row r="334">
@@ -4686,7 +4680,7 @@
         <v>16</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.385691882904305</v>
       </c>
     </row>
     <row r="336">
@@ -4719,7 +4713,7 @@
         <v>16</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.298530735364884</v>
       </c>
     </row>
     <row r="339">
@@ -4785,7 +4779,7 @@
         <v>16</v>
       </c>
       <c r="C344" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.191654733671662</v>
       </c>
     </row>
     <row r="345">
@@ -4807,7 +4801,7 @@
         <v>16</v>
       </c>
       <c r="C346" t="n">
-        <v>-0.160584352265163</v>
+        <v>-0.164806341519887</v>
       </c>
     </row>
     <row r="347">
@@ -4818,7 +4812,7 @@
         <v>16</v>
       </c>
       <c r="C347" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.440798917615077</v>
       </c>
     </row>
     <row r="348">
@@ -4840,7 +4834,7 @@
         <v>16</v>
       </c>
       <c r="C349" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.253478366673776</v>
       </c>
     </row>
     <row r="350">
@@ -4851,7 +4845,7 @@
         <v>16</v>
       </c>
       <c r="C350" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.17662809958042</v>
       </c>
     </row>
     <row r="351">
@@ -4862,7 +4856,7 @@
         <v>16</v>
       </c>
       <c r="C351" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.305239171947161</v>
       </c>
     </row>
     <row r="352">
@@ -4873,7 +4867,7 @@
         <v>16</v>
       </c>
       <c r="C352" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.188601818445983</v>
       </c>
     </row>
     <row r="353">
@@ -4895,7 +4889,7 @@
         <v>16</v>
       </c>
       <c r="C354" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.248165118405095</v>
       </c>
     </row>
     <row r="355">
@@ -4906,7 +4900,7 @@
         <v>16</v>
       </c>
       <c r="C355" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.23236444867808</v>
       </c>
     </row>
     <row r="356">
@@ -4917,7 +4911,7 @@
         <v>16</v>
       </c>
       <c r="C356" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.318565216628055</v>
       </c>
     </row>
     <row r="357">
@@ -4928,7 +4922,7 @@
         <v>16</v>
       </c>
       <c r="C357" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.707946680312046</v>
       </c>
     </row>
     <row r="358">
@@ -4950,7 +4944,7 @@
         <v>16</v>
       </c>
       <c r="C359" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.176763521464026</v>
       </c>
     </row>
     <row r="360">
@@ -4961,7 +4955,7 @@
         <v>16</v>
       </c>
       <c r="C360" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.20111585048214</v>
       </c>
     </row>
     <row r="361">
@@ -4983,7 +4977,7 @@
         <v>16</v>
       </c>
       <c r="C362" t="n">
-        <v>-0.165936709464264</v>
+        <v>-0.143062501784387</v>
       </c>
     </row>
     <row r="363">
@@ -5016,7 +5010,7 @@
         <v>16</v>
       </c>
       <c r="C365" t="n">
-        <v>-0.169549113204387</v>
+        <v>-0.327751277406481</v>
       </c>
     </row>
     <row r="366">
@@ -5027,7 +5021,7 @@
         <v>16</v>
       </c>
       <c r="C366" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.205193952768561</v>
       </c>
     </row>
     <row r="367">
@@ -5104,7 +5098,7 @@
         <v>16</v>
       </c>
       <c r="C373" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.173134152972348</v>
       </c>
     </row>
     <row r="374">
@@ -5126,7 +5120,7 @@
         <v>16</v>
       </c>
       <c r="C375" t="n">
-        <v>-0.162700644609379</v>
+        <v>-0.163981119881359</v>
       </c>
     </row>
     <row r="376">
@@ -5137,7 +5131,7 @@
         <v>16</v>
       </c>
       <c r="C376" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.197879134037153</v>
       </c>
     </row>
     <row r="377">
@@ -5148,7 +5142,7 @@
         <v>16</v>
       </c>
       <c r="C377" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.193623463818704</v>
       </c>
     </row>
     <row r="378">
@@ -5170,7 +5164,7 @@
         <v>16</v>
       </c>
       <c r="C379" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.265083839451064</v>
       </c>
     </row>
     <row r="380">
@@ -5181,7 +5175,7 @@
         <v>16</v>
       </c>
       <c r="C380" t="n">
-        <v>-0.161414036505047</v>
+        <v>-0.179543986719816</v>
       </c>
     </row>
     <row r="381">
@@ -5192,7 +5186,7 @@
         <v>16</v>
       </c>
       <c r="C381" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.279703006635752</v>
       </c>
     </row>
     <row r="382">
@@ -5203,7 +5197,7 @@
         <v>16</v>
       </c>
       <c r="C382" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.164549235742012</v>
       </c>
     </row>
     <row r="383">
@@ -5247,7 +5241,7 @@
         <v>16</v>
       </c>
       <c r="C386" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.142515188081548</v>
       </c>
     </row>
     <row r="387">
@@ -5258,7 +5252,7 @@
         <v>16</v>
       </c>
       <c r="C387" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.384441027611773</v>
       </c>
     </row>
     <row r="388">
@@ -5269,7 +5263,7 @@
         <v>16</v>
       </c>
       <c r="C388" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.623598498566722</v>
       </c>
     </row>
     <row r="389">
@@ -5291,7 +5285,7 @@
         <v>16</v>
       </c>
       <c r="C390" t="n">
-        <v>-0.0890617858408813</v>
+        <v>0.315375304422704</v>
       </c>
     </row>
     <row r="391">
@@ -5302,7 +5296,7 @@
         <v>16</v>
       </c>
       <c r="C391" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.209582729456103</v>
       </c>
     </row>
     <row r="392">
@@ -5313,7 +5307,7 @@
         <v>16</v>
       </c>
       <c r="C392" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.417801401142558</v>
       </c>
     </row>
     <row r="393">
@@ -5401,7 +5395,7 @@
         <v>16</v>
       </c>
       <c r="C400" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.307782195595761</v>
       </c>
     </row>
     <row r="401">
@@ -5423,7 +5417,7 @@
         <v>16</v>
       </c>
       <c r="C402" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.786371562351342</v>
       </c>
     </row>
     <row r="403">
@@ -5434,7 +5428,7 @@
         <v>16</v>
       </c>
       <c r="C403" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.14002902976982</v>
       </c>
     </row>
     <row r="404">
@@ -5445,7 +5439,7 @@
         <v>16</v>
       </c>
       <c r="C404" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.265337712797675</v>
       </c>
     </row>
     <row r="405">
@@ -5456,7 +5450,7 @@
         <v>16</v>
       </c>
       <c r="C405" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.525643179119484</v>
       </c>
     </row>
     <row r="406">
@@ -5478,7 +5472,7 @@
         <v>16</v>
       </c>
       <c r="C407" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.042753951265124</v>
       </c>
     </row>
     <row r="408">
@@ -5544,7 +5538,7 @@
         <v>16</v>
       </c>
       <c r="C413" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.274203229334678</v>
       </c>
     </row>
     <row r="414">
@@ -5566,7 +5560,7 @@
         <v>16</v>
       </c>
       <c r="C415" t="n">
-        <v>-0.166228629466938</v>
+        <v>-0.347152480181385</v>
       </c>
     </row>
     <row r="416">
@@ -5588,7 +5582,7 @@
         <v>16</v>
       </c>
       <c r="C417" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.162123006771004</v>
       </c>
     </row>
     <row r="418">
@@ -5599,7 +5593,7 @@
         <v>16</v>
       </c>
       <c r="C418" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.173540453405742</v>
       </c>
     </row>
     <row r="419">
@@ -5709,7 +5703,7 @@
         <v>16</v>
       </c>
       <c r="C428" t="n">
-        <v>-0.176585390999757</v>
+        <v>-0.0828231761476381</v>
       </c>
     </row>
     <row r="429">
@@ -5720,7 +5714,7 @@
         <v>16</v>
       </c>
       <c r="C429" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.0342001052184759</v>
       </c>
     </row>
     <row r="430">
@@ -5731,7 +5725,7 @@
         <v>16</v>
       </c>
       <c r="C430" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.425400937508487</v>
       </c>
     </row>
     <row r="431">
@@ -5742,7 +5736,7 @@
         <v>16</v>
       </c>
       <c r="C431" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.695417983484169</v>
       </c>
     </row>
     <row r="432">
@@ -5775,7 +5769,7 @@
         <v>16</v>
       </c>
       <c r="C434" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.305992099663033</v>
       </c>
     </row>
     <row r="435">
@@ -5786,7 +5780,7 @@
         <v>16</v>
       </c>
       <c r="C435" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.507066265513593</v>
       </c>
     </row>
     <row r="436">
@@ -5819,7 +5813,7 @@
         <v>16</v>
       </c>
       <c r="C438" t="n">
-        <v>-0.163079850929012</v>
+        <v>-0.226933663650629</v>
       </c>
     </row>
     <row r="439">
@@ -5830,7 +5824,7 @@
         <v>16</v>
       </c>
       <c r="C439" t="n">
-        <v>-0.154521211836192</v>
+        <v>-0.212454416739252</v>
       </c>
     </row>
     <row r="440">
@@ -5885,7 +5879,7 @@
         <v>16</v>
       </c>
       <c r="C444" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.447979551358626</v>
       </c>
     </row>
     <row r="445">
@@ -5918,7 +5912,7 @@
         <v>16</v>
       </c>
       <c r="C447" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.263612066438356</v>
       </c>
     </row>
     <row r="448">
@@ -6006,7 +6000,7 @@
         <v>16</v>
       </c>
       <c r="C455" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.20422138896116</v>
       </c>
     </row>
     <row r="456">
@@ -6105,7 +6099,7 @@
         <v>16</v>
       </c>
       <c r="C464" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.176018028373457</v>
       </c>
     </row>
     <row r="465">
@@ -6116,7 +6110,7 @@
         <v>16</v>
       </c>
       <c r="C465" t="n">
-        <v>-0.168486852513184</v>
+        <v>-0.257025455875595</v>
       </c>
     </row>
     <row r="466">
@@ -6138,7 +6132,7 @@
         <v>16</v>
       </c>
       <c r="C467" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.285071802014244</v>
       </c>
     </row>
     <row r="468">
@@ -6149,7 +6143,7 @@
         <v>16</v>
       </c>
       <c r="C468" t="n">
-        <v>-0.16735676883557</v>
+        <v>-0.681550141985242</v>
       </c>
     </row>
     <row r="469">
@@ -6248,7 +6242,7 @@
         <v>16</v>
       </c>
       <c r="C477" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.338138063999011</v>
       </c>
     </row>
     <row r="478">
@@ -6336,7 +6330,7 @@
         <v>16</v>
       </c>
       <c r="C485" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.589534232457248</v>
       </c>
     </row>
     <row r="486">
@@ -6347,7 +6341,7 @@
         <v>16</v>
       </c>
       <c r="C486" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.170385431446005</v>
       </c>
     </row>
     <row r="487">
@@ -6358,7 +6352,7 @@
         <v>16</v>
       </c>
       <c r="C487" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.187273709115411</v>
       </c>
     </row>
     <row r="488">
@@ -6369,7 +6363,7 @@
         <v>16</v>
       </c>
       <c r="C488" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.210258331116713</v>
       </c>
     </row>
     <row r="489">
@@ -6380,7 +6374,7 @@
         <v>16</v>
       </c>
       <c r="C489" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.398142188983162</v>
       </c>
     </row>
     <row r="490">
@@ -6391,7 +6385,7 @@
         <v>16</v>
       </c>
       <c r="C490" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.159085320211996</v>
       </c>
     </row>
     <row r="491">
@@ -6435,7 +6429,7 @@
         <v>16</v>
       </c>
       <c r="C494" t="n">
-        <v>-0.172963230672877</v>
+        <v>-0.389852555015628</v>
       </c>
     </row>
     <row r="495">
@@ -6468,7 +6462,7 @@
         <v>16</v>
       </c>
       <c r="C497" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.183181351340522</v>
       </c>
     </row>
     <row r="498">
@@ -6490,7 +6484,7 @@
         <v>16</v>
       </c>
       <c r="C499" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.164193546574889</v>
       </c>
     </row>
     <row r="500">
@@ -6501,7 +6495,7 @@
         <v>16</v>
       </c>
       <c r="C500" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.327320066351517</v>
       </c>
     </row>
     <row r="501">
@@ -6512,7 +6506,7 @@
         <v>16</v>
       </c>
       <c r="C501" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.163303881836528</v>
       </c>
     </row>
     <row r="502">
@@ -6545,7 +6539,7 @@
         <v>16</v>
       </c>
       <c r="C504" t="n">
-        <v>-0.168715428787327</v>
+        <v>-0.134619140061657</v>
       </c>
     </row>
     <row r="505">
@@ -6600,7 +6594,7 @@
         <v>16</v>
       </c>
       <c r="C509" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.440172300677705</v>
       </c>
     </row>
     <row r="510">
@@ -6611,7 +6605,7 @@
         <v>16</v>
       </c>
       <c r="C510" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.395363913614662</v>
       </c>
     </row>
     <row r="511">
@@ -6644,7 +6638,7 @@
         <v>16</v>
       </c>
       <c r="C513" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.162061367989891</v>
       </c>
     </row>
     <row r="514">
@@ -6677,7 +6671,7 @@
         <v>16</v>
       </c>
       <c r="C516" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.482863699954086</v>
       </c>
     </row>
     <row r="517">
@@ -6699,7 +6693,7 @@
         <v>16</v>
       </c>
       <c r="C518" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.375966734998382</v>
       </c>
     </row>
     <row r="519">
@@ -6710,7 +6704,7 @@
         <v>16</v>
       </c>
       <c r="C519" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.323212142495346</v>
       </c>
     </row>
     <row r="520">
@@ -6732,7 +6726,7 @@
         <v>16</v>
       </c>
       <c r="C521" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.360885568485694</v>
       </c>
     </row>
     <row r="522">
@@ -6754,7 +6748,7 @@
         <v>16</v>
       </c>
       <c r="C523" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.159203789868154</v>
       </c>
     </row>
     <row r="524">
@@ -6765,7 +6759,7 @@
         <v>16</v>
       </c>
       <c r="C524" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.288017698594953</v>
       </c>
     </row>
     <row r="525">
@@ -6809,7 +6803,7 @@
         <v>16</v>
       </c>
       <c r="C528" t="n">
-        <v>-0.164414353284555</v>
+        <v>-0.560357766554407</v>
       </c>
     </row>
     <row r="529">
@@ -6820,7 +6814,7 @@
         <v>16</v>
       </c>
       <c r="C529" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.10739198783277</v>
       </c>
     </row>
     <row r="530">
@@ -6842,7 +6836,7 @@
         <v>16</v>
       </c>
       <c r="C531" t="n">
-        <v>-0.160729504150207</v>
+        <v>-0.392462648649686</v>
       </c>
     </row>
     <row r="532">
@@ -6853,7 +6847,7 @@
         <v>16</v>
       </c>
       <c r="C532" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.226444891158033</v>
       </c>
     </row>
     <row r="533">
@@ -6886,7 +6880,7 @@
         <v>16</v>
       </c>
       <c r="C535" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.32959243173474</v>
       </c>
     </row>
     <row r="536">
@@ -6908,7 +6902,7 @@
         <v>16</v>
       </c>
       <c r="C537" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.325218816121762</v>
       </c>
     </row>
     <row r="538">
@@ -6919,7 +6913,7 @@
         <v>16</v>
       </c>
       <c r="C538" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.35140566825767</v>
       </c>
     </row>
     <row r="539">
@@ -6985,7 +6979,7 @@
         <v>16</v>
       </c>
       <c r="C544" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.108932233214731</v>
       </c>
     </row>
     <row r="545">
@@ -7018,7 +7012,7 @@
         <v>16</v>
       </c>
       <c r="C547" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.64829761326273</v>
       </c>
     </row>
     <row r="548">
@@ -7040,7 +7034,7 @@
         <v>16</v>
       </c>
       <c r="C549" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.240524187320243</v>
       </c>
     </row>
     <row r="550">
@@ -7051,7 +7045,7 @@
         <v>16</v>
       </c>
       <c r="C550" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.166991343142687</v>
       </c>
     </row>
     <row r="551">
@@ -7073,7 +7067,7 @@
         <v>16</v>
       </c>
       <c r="C552" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.190942141918558</v>
       </c>
     </row>
     <row r="553">
@@ -7095,7 +7089,7 @@
         <v>16</v>
       </c>
       <c r="C554" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.340322401796436</v>
       </c>
     </row>
     <row r="555">
@@ -7106,7 +7100,7 @@
         <v>16</v>
       </c>
       <c r="C555" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.243393477424035</v>
       </c>
     </row>
     <row r="556">
@@ -7128,7 +7122,7 @@
         <v>16</v>
       </c>
       <c r="C557" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.965359138029564</v>
       </c>
     </row>
     <row r="558">
@@ -7161,7 +7155,7 @@
         <v>16</v>
       </c>
       <c r="C560" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.427760427460875</v>
       </c>
     </row>
     <row r="561">
@@ -7183,7 +7177,7 @@
         <v>16</v>
       </c>
       <c r="C562" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.345200669170042</v>
       </c>
     </row>
     <row r="563">
@@ -7205,7 +7199,7 @@
         <v>16</v>
       </c>
       <c r="C564" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.482368149943472</v>
       </c>
     </row>
     <row r="565">
@@ -7216,7 +7210,7 @@
         <v>16</v>
       </c>
       <c r="C565" t="n">
-        <v>-0.162437775437369</v>
+        <v>-0.262182153712297</v>
       </c>
     </row>
     <row r="566">
@@ -7227,7 +7221,7 @@
         <v>16</v>
       </c>
       <c r="C566" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.192740692143291</v>
       </c>
     </row>
     <row r="567">
@@ -7238,7 +7232,7 @@
         <v>16</v>
       </c>
       <c r="C567" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.169736367398067</v>
       </c>
     </row>
     <row r="568">
@@ -7304,7 +7298,7 @@
         <v>16</v>
       </c>
       <c r="C573" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.165098492624612</v>
       </c>
     </row>
     <row r="574">
@@ -7315,7 +7309,7 @@
         <v>16</v>
       </c>
       <c r="C574" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.197909187401366</v>
       </c>
     </row>
     <row r="575">
@@ -7326,7 +7320,7 @@
         <v>16</v>
       </c>
       <c r="C575" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.301954292644305</v>
       </c>
     </row>
     <row r="576">
@@ -7337,7 +7331,7 @@
         <v>16</v>
       </c>
       <c r="C576" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.182095032221854</v>
       </c>
     </row>
     <row r="577">
@@ -7348,7 +7342,7 @@
         <v>16</v>
       </c>
       <c r="C577" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.327951017703371</v>
       </c>
     </row>
     <row r="578">
@@ -7370,7 +7364,7 @@
         <v>16</v>
       </c>
       <c r="C579" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.390752636687348</v>
       </c>
     </row>
     <row r="580">
@@ -7381,7 +7375,7 @@
         <v>16</v>
       </c>
       <c r="C580" t="n">
-        <v>-0.175755530183688</v>
+        <v>-0.216288619243159</v>
       </c>
     </row>
     <row r="581">
@@ -7436,7 +7430,7 @@
         <v>16</v>
       </c>
       <c r="C585" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.204818988613533</v>
       </c>
     </row>
     <row r="586">
@@ -7447,7 +7441,7 @@
         <v>16</v>
       </c>
       <c r="C586" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.257915056728261</v>
       </c>
     </row>
     <row r="587">
@@ -7469,7 +7463,7 @@
         <v>16</v>
       </c>
       <c r="C588" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.309621426237602</v>
       </c>
     </row>
     <row r="589">
@@ -7491,7 +7485,7 @@
         <v>16</v>
       </c>
       <c r="C590" t="n">
-        <v>-0.156880977103394</v>
+        <v>0.251403014667752</v>
       </c>
     </row>
     <row r="591">
@@ -7502,7 +7496,7 @@
         <v>16</v>
       </c>
       <c r="C591" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.169431733271588</v>
       </c>
     </row>
     <row r="592">
@@ -7601,7 +7595,7 @@
         <v>16</v>
       </c>
       <c r="C600" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.289629020589158</v>
       </c>
     </row>
     <row r="601">
@@ -7634,7 +7628,7 @@
         <v>16</v>
       </c>
       <c r="C603" t="n">
-        <v>-0.163623115195793</v>
+        <v>-0.343936992508497</v>
       </c>
     </row>
     <row r="604">
@@ -7645,7 +7639,7 @@
         <v>16</v>
       </c>
       <c r="C604" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.152501890150437</v>
       </c>
     </row>
     <row r="605">
@@ -7667,7 +7661,7 @@
         <v>16</v>
       </c>
       <c r="C606" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.490416602318876</v>
       </c>
     </row>
     <row r="607">
@@ -7678,7 +7672,7 @@
         <v>16</v>
       </c>
       <c r="C607" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.278370722457499</v>
       </c>
     </row>
     <row r="608">
@@ -7711,7 +7705,7 @@
         <v>16</v>
       </c>
       <c r="C610" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.194705894721354</v>
       </c>
     </row>
     <row r="611">
@@ -7733,7 +7727,7 @@
         <v>16</v>
       </c>
       <c r="C612" t="n">
-        <v>-0.156566562600482</v>
+        <v>-0.157543990597979</v>
       </c>
     </row>
     <row r="613">
@@ -7777,7 +7771,7 @@
         <v>16</v>
       </c>
       <c r="C616" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.303104448838568</v>
       </c>
     </row>
     <row r="617">
@@ -7799,7 +7793,7 @@
         <v>16</v>
       </c>
       <c r="C618" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.176849000803352</v>
       </c>
     </row>
     <row r="619">
@@ -7854,7 +7848,7 @@
         <v>16</v>
       </c>
       <c r="C623" t="n">
-        <v>-0.158474001016336</v>
+        <v>-0.217018715269131</v>
       </c>
     </row>
     <row r="624">
@@ -7865,7 +7859,7 @@
         <v>16</v>
       </c>
       <c r="C624" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.46901087728315</v>
       </c>
     </row>
     <row r="625">
@@ -7887,7 +7881,7 @@
         <v>16</v>
       </c>
       <c r="C626" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.161001498346797</v>
       </c>
     </row>
     <row r="627">
@@ -7898,7 +7892,7 @@
         <v>16</v>
       </c>
       <c r="C627" t="n">
-        <v>-0.158662105936844</v>
+        <v>-0.178899520943582</v>
       </c>
     </row>
     <row r="628">
@@ -7953,7 +7947,7 @@
         <v>16</v>
       </c>
       <c r="C632" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.275978053431602</v>
       </c>
     </row>
     <row r="633">
@@ -8019,7 +8013,7 @@
         <v>16</v>
       </c>
       <c r="C638" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.164431442113549</v>
       </c>
     </row>
     <row r="639">
@@ -8052,7 +8046,7 @@
         <v>16</v>
       </c>
       <c r="C641" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.375483191530732</v>
       </c>
     </row>
     <row r="642">
@@ -8074,7 +8068,7 @@
         <v>16</v>
       </c>
       <c r="C643" t="n">
-        <v>-0.160863320773418</v>
+        <v>-0.0861529325003192</v>
       </c>
     </row>
     <row r="644">
@@ -8096,7 +8090,7 @@
         <v>16</v>
       </c>
       <c r="C645" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.206752817317509</v>
       </c>
     </row>
     <row r="646">
@@ -8107,7 +8101,7 @@
         <v>16</v>
       </c>
       <c r="C646" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.248391613410655</v>
       </c>
     </row>
     <row r="647">
@@ -8118,7 +8112,7 @@
         <v>16</v>
       </c>
       <c r="C647" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.423855028754687</v>
       </c>
     </row>
     <row r="648">
@@ -8129,7 +8123,7 @@
         <v>16</v>
       </c>
       <c r="C648" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.183309184232775</v>
       </c>
     </row>
     <row r="649">
@@ -8140,7 +8134,7 @@
         <v>16</v>
       </c>
       <c r="C649" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.123923640685119</v>
       </c>
     </row>
     <row r="650">
@@ -8162,7 +8156,7 @@
         <v>16</v>
       </c>
       <c r="C651" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.370700395648327</v>
       </c>
     </row>
     <row r="652">
@@ -8217,7 +8211,7 @@
         <v>16</v>
       </c>
       <c r="C656" t="n">
-        <v>-0.159105753739963</v>
+        <v>-0.401288262473545</v>
       </c>
     </row>
     <row r="657">
@@ -8261,7 +8255,7 @@
         <v>16</v>
       </c>
       <c r="C660" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.371846611863408</v>
       </c>
     </row>
     <row r="661">
@@ -8272,7 +8266,7 @@
         <v>16</v>
       </c>
       <c r="C661" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.150962429143792</v>
       </c>
     </row>
     <row r="662">
@@ -8283,7 +8277,7 @@
         <v>16</v>
       </c>
       <c r="C662" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.254570188501412</v>
       </c>
     </row>
     <row r="663">
@@ -8327,7 +8321,7 @@
         <v>16</v>
       </c>
       <c r="C666" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.181604995985204</v>
       </c>
     </row>
     <row r="667">
@@ -8393,7 +8387,7 @@
         <v>16</v>
       </c>
       <c r="C672" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.306825861635523</v>
       </c>
     </row>
     <row r="673">
@@ -8426,7 +8420,7 @@
         <v>16</v>
       </c>
       <c r="C675" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.133486846164219</v>
       </c>
     </row>
     <row r="676">
@@ -8448,7 +8442,7 @@
         <v>16</v>
       </c>
       <c r="C677" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.767584813388943</v>
       </c>
     </row>
     <row r="678">
@@ -8481,7 +8475,7 @@
         <v>16</v>
       </c>
       <c r="C680" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.152516445119774</v>
       </c>
     </row>
     <row r="681">
@@ -8492,7 +8486,7 @@
         <v>16</v>
       </c>
       <c r="C681" t="n">
-        <v>-0.160060636996487</v>
+        <v>-0.175831656992351</v>
       </c>
     </row>
     <row r="682">
@@ -8514,7 +8508,7 @@
         <v>16</v>
       </c>
       <c r="C683" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.15899956081966</v>
       </c>
     </row>
     <row r="684">
@@ -8536,7 +8530,7 @@
         <v>16</v>
       </c>
       <c r="C685" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.642093578733736</v>
       </c>
     </row>
     <row r="686">
@@ -8547,7 +8541,7 @@
         <v>16</v>
       </c>
       <c r="C686" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.17473067528321</v>
       </c>
     </row>
     <row r="687">
@@ -8580,7 +8574,7 @@
         <v>16</v>
       </c>
       <c r="C689" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.160716792223274</v>
       </c>
     </row>
     <row r="690">
@@ -8591,7 +8585,7 @@
         <v>16</v>
       </c>
       <c r="C690" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.32863459826115</v>
       </c>
     </row>
     <row r="691">
@@ -8602,7 +8596,7 @@
         <v>16</v>
       </c>
       <c r="C691" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.189347295941468</v>
       </c>
     </row>
     <row r="692">
@@ -8613,7 +8607,7 @@
         <v>16</v>
       </c>
       <c r="C692" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.20844558546972</v>
       </c>
     </row>
     <row r="693">
@@ -8657,7 +8651,7 @@
         <v>16</v>
       </c>
       <c r="C696" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.209480335969058</v>
       </c>
     </row>
     <row r="697">
@@ -8668,7 +8662,7 @@
         <v>16</v>
       </c>
       <c r="C697" t="n">
-        <v>-0.160892200336087</v>
+        <v>0.000901468963319108</v>
       </c>
     </row>
     <row r="698">
@@ -8767,7 +8761,7 @@
         <v>16</v>
       </c>
       <c r="C706" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.206644040041912</v>
       </c>
     </row>
     <row r="707">
@@ -8778,7 +8772,7 @@
         <v>16</v>
       </c>
       <c r="C707" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.184757445305845</v>
       </c>
     </row>
     <row r="708">
@@ -8811,7 +8805,7 @@
         <v>16</v>
       </c>
       <c r="C710" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.456662174333421</v>
       </c>
     </row>
     <row r="711">
@@ -8888,7 +8882,7 @@
         <v>16</v>
       </c>
       <c r="C717" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.391847340154182</v>
       </c>
     </row>
     <row r="718">
@@ -8899,7 +8893,7 @@
         <v>16</v>
       </c>
       <c r="C718" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.472761732649137</v>
       </c>
     </row>
     <row r="719">
@@ -8910,7 +8904,7 @@
         <v>16</v>
       </c>
       <c r="C719" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.0334591820852002</v>
       </c>
     </row>
     <row r="720">
@@ -8954,7 +8948,7 @@
         <v>16</v>
       </c>
       <c r="C723" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.237472908755464</v>
       </c>
     </row>
     <row r="724">
@@ -8976,7 +8970,7 @@
         <v>16</v>
       </c>
       <c r="C725" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.265602532902664</v>
       </c>
     </row>
     <row r="726">
@@ -9064,7 +9058,7 @@
         <v>16</v>
       </c>
       <c r="C733" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.517374589742963</v>
       </c>
     </row>
     <row r="734">
@@ -9152,7 +9146,7 @@
         <v>16</v>
       </c>
       <c r="C741" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.186806842530385</v>
       </c>
     </row>
     <row r="742">
@@ -9163,7 +9157,7 @@
         <v>16</v>
       </c>
       <c r="C742" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.559855162013334</v>
       </c>
     </row>
     <row r="743">
@@ -9174,7 +9168,7 @@
         <v>16</v>
       </c>
       <c r="C743" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.181147913244148</v>
       </c>
     </row>
     <row r="744">
@@ -9185,7 +9179,7 @@
         <v>16</v>
       </c>
       <c r="C744" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.339495949184549</v>
       </c>
     </row>
     <row r="745">
@@ -9196,7 +9190,7 @@
         <v>16</v>
       </c>
       <c r="C745" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.218861236111969</v>
       </c>
     </row>
     <row r="746">
@@ -9218,7 +9212,7 @@
         <v>16</v>
       </c>
       <c r="C747" t="n">
-        <v>-0.174916346179223</v>
+        <v>-0.31632624545838</v>
       </c>
     </row>
     <row r="748">
@@ -9251,7 +9245,7 @@
         <v>16</v>
       </c>
       <c r="C750" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.260772132573396</v>
       </c>
     </row>
     <row r="751">
@@ -9273,7 +9267,7 @@
         <v>16</v>
       </c>
       <c r="C752" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.216159445481202</v>
       </c>
     </row>
     <row r="753">
@@ -9405,7 +9399,7 @@
         <v>16</v>
       </c>
       <c r="C764" t="n">
-        <v>-0.158439184265034</v>
+        <v>-0.154614286222647</v>
       </c>
     </row>
     <row r="765">
@@ -9427,7 +9421,7 @@
         <v>16</v>
       </c>
       <c r="C766" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.211009871290303</v>
       </c>
     </row>
     <row r="767">
@@ -9438,7 +9432,7 @@
         <v>16</v>
       </c>
       <c r="C767" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.152191986689668</v>
       </c>
     </row>
     <row r="768">
@@ -9460,7 +9454,7 @@
         <v>16</v>
       </c>
       <c r="C769" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.195375273005413</v>
       </c>
     </row>
     <row r="770">
@@ -9482,7 +9476,7 @@
         <v>16</v>
       </c>
       <c r="C771" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.269691808192555</v>
       </c>
     </row>
     <row r="772">
@@ -9504,7 +9498,7 @@
         <v>16</v>
       </c>
       <c r="C773" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.354222543694371</v>
       </c>
     </row>
     <row r="774">
@@ -9515,7 +9509,7 @@
         <v>16</v>
       </c>
       <c r="C774" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.264883859032914</v>
       </c>
     </row>
     <row r="775">
@@ -9526,7 +9520,7 @@
         <v>16</v>
       </c>
       <c r="C775" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.175981308194279</v>
       </c>
     </row>
     <row r="776">
@@ -9581,7 +9575,7 @@
         <v>16</v>
       </c>
       <c r="C780" t="n">
-        <v>-0.159709246024664</v>
+        <v>0.158075120476379</v>
       </c>
     </row>
     <row r="781">
@@ -9614,7 +9608,7 @@
         <v>16</v>
       </c>
       <c r="C783" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.505697846220212</v>
       </c>
     </row>
     <row r="784">
@@ -9625,7 +9619,7 @@
         <v>16</v>
       </c>
       <c r="C784" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.244636717166468</v>
       </c>
     </row>
     <row r="785">
@@ -9658,7 +9652,7 @@
         <v>16</v>
       </c>
       <c r="C787" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.613653583630923</v>
       </c>
     </row>
     <row r="788">
@@ -9713,7 +9707,7 @@
         <v>16</v>
       </c>
       <c r="C792" t="n">
-        <v>-0.160854757334444</v>
+        <v>-0.16926189025608</v>
       </c>
     </row>
     <row r="793">
@@ -9746,7 +9740,7 @@
         <v>16</v>
       </c>
       <c r="C795" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.0197855713244328</v>
       </c>
     </row>
     <row r="796">
@@ -9757,7 +9751,7 @@
         <v>16</v>
       </c>
       <c r="C796" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.10000207772498</v>
       </c>
     </row>
     <row r="797">
@@ -9801,7 +9795,7 @@
         <v>16</v>
       </c>
       <c r="C800" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.286113754319607</v>
       </c>
     </row>
     <row r="801">
@@ -9812,7 +9806,7 @@
         <v>16</v>
       </c>
       <c r="C801" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.144734616177418</v>
       </c>
     </row>
     <row r="802">
@@ -9823,7 +9817,7 @@
         <v>16</v>
       </c>
       <c r="C802" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.162168395319743</v>
       </c>
     </row>
     <row r="803">
@@ -9845,7 +9839,7 @@
         <v>16</v>
       </c>
       <c r="C804" t="n">
-        <v>-0.174955953771671</v>
+        <v>-0.196931972181809</v>
       </c>
     </row>
     <row r="805">
@@ -9867,7 +9861,7 @@
         <v>16</v>
       </c>
       <c r="C806" t="n">
-        <v>-0.165538615043252</v>
+        <v>-0.182323754211167</v>
       </c>
     </row>
     <row r="807">
@@ -9878,7 +9872,7 @@
         <v>16</v>
       </c>
       <c r="C807" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.367987907905589</v>
       </c>
     </row>
     <row r="808">
@@ -9889,7 +9883,7 @@
         <v>16</v>
       </c>
       <c r="C808" t="n">
-        <v>-0.173890387902206</v>
+        <v>-0.247788427020132</v>
       </c>
     </row>
     <row r="809">
@@ -9900,7 +9894,7 @@
         <v>16</v>
       </c>
       <c r="C809" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.194960191762923</v>
       </c>
     </row>
     <row r="810">
@@ -9911,7 +9905,7 @@
         <v>16</v>
       </c>
       <c r="C810" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.159973846755471</v>
       </c>
     </row>
     <row r="811">
@@ -9922,7 +9916,7 @@
         <v>16</v>
       </c>
       <c r="C811" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.530971721090754</v>
       </c>
     </row>
     <row r="812">
@@ -9933,7 +9927,7 @@
         <v>16</v>
       </c>
       <c r="C812" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.260083309753844</v>
       </c>
     </row>
     <row r="813">
@@ -9944,7 +9938,7 @@
         <v>16</v>
       </c>
       <c r="C813" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.401919396878707</v>
       </c>
     </row>
     <row r="814">
@@ -9966,7 +9960,7 @@
         <v>16</v>
       </c>
       <c r="C815" t="n">
-        <v>-0.176023695110149</v>
+        <v>-0.0673912022005334</v>
       </c>
     </row>
     <row r="816">
@@ -9999,7 +9993,7 @@
         <v>16</v>
       </c>
       <c r="C818" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.212917605062681</v>
       </c>
     </row>
     <row r="819">
@@ -10010,7 +10004,7 @@
         <v>16</v>
       </c>
       <c r="C819" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.19925566372904</v>
       </c>
     </row>
     <row r="820">
@@ -10032,7 +10026,7 @@
         <v>16</v>
       </c>
       <c r="C821" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.254963143565802</v>
       </c>
     </row>
     <row r="822">
@@ -10054,7 +10048,7 @@
         <v>16</v>
       </c>
       <c r="C823" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.222893610369954</v>
       </c>
     </row>
     <row r="824">
@@ -10065,7 +10059,7 @@
         <v>16</v>
       </c>
       <c r="C824" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.169490507687141</v>
       </c>
     </row>
     <row r="825">
@@ -10076,7 +10070,7 @@
         <v>16</v>
       </c>
       <c r="C825" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.575026743954254</v>
       </c>
     </row>
     <row r="826">
@@ -10109,7 +10103,7 @@
         <v>16</v>
       </c>
       <c r="C828" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.240028469316493</v>
       </c>
     </row>
     <row r="829">
@@ -10142,7 +10136,7 @@
         <v>16</v>
       </c>
       <c r="C831" t="n">
-        <v>-0.171752339770339</v>
+        <v>-0.195773295452313</v>
       </c>
     </row>
     <row r="832">
@@ -10153,7 +10147,7 @@
         <v>16</v>
       </c>
       <c r="C832" t="n">
-        <v>-0.161973294299376</v>
+        <v>-0.284255702273059</v>
       </c>
     </row>
     <row r="833">
@@ -10164,7 +10158,7 @@
         <v>16</v>
       </c>
       <c r="C833" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.167484340229572</v>
       </c>
     </row>
     <row r="834">
@@ -10186,7 +10180,7 @@
         <v>16</v>
       </c>
       <c r="C835" t="n">
-        <v>-0.14568320804364</v>
+        <v>-0.140048869345742</v>
       </c>
     </row>
     <row r="836">
@@ -10197,7 +10191,7 @@
         <v>16</v>
       </c>
       <c r="C836" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.180101697062121</v>
       </c>
     </row>
     <row r="837">
@@ -10208,7 +10202,7 @@
         <v>16</v>
       </c>
       <c r="C837" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.210088792658003</v>
       </c>
     </row>
     <row r="838">
@@ -10230,7 +10224,7 @@
         <v>16</v>
       </c>
       <c r="C839" t="n">
-        <v>-0.177251924372478</v>
+        <v>-0.162048372254346</v>
       </c>
     </row>
     <row r="840">
@@ -10252,7 +10246,7 @@
         <v>16</v>
       </c>
       <c r="C841" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.408300945908682</v>
       </c>
     </row>
     <row r="842">
@@ -10274,7 +10268,7 @@
         <v>16</v>
       </c>
       <c r="C843" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.204987915038358</v>
       </c>
     </row>
     <row r="844">
@@ -10307,7 +10301,7 @@
         <v>16</v>
       </c>
       <c r="C846" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.407515679177803</v>
       </c>
     </row>
     <row r="847">
@@ -10318,7 +10312,7 @@
         <v>16</v>
       </c>
       <c r="C847" t="n">
-        <v>-0.174674811658648</v>
+        <v>-0.574147799816614</v>
       </c>
     </row>
     <row r="848">
@@ -10351,7 +10345,7 @@
         <v>16</v>
       </c>
       <c r="C850" t="n">
-        <v>-0.17411888924736</v>
+        <v>-0.278704781692226</v>
       </c>
     </row>
     <row r="851">
@@ -10395,7 +10389,7 @@
         <v>16</v>
       </c>
       <c r="C854" t="n">
-        <v>-0.168002855872445</v>
+        <v>0.556972974184096</v>
       </c>
     </row>
     <row r="855">
@@ -10406,7 +10400,7 @@
         <v>16</v>
       </c>
       <c r="C855" t="n">
-        <v>-0.163825057771841</v>
+        <v>-0.248694995088213</v>
       </c>
     </row>
     <row r="856">
@@ -10439,7 +10433,7 @@
         <v>16</v>
       </c>
       <c r="C858" t="n">
-        <v>-0.189455862970212</v>
+        <v>-0.217017948051268</v>
       </c>
     </row>
     <row r="859">
@@ -10450,7 +10444,7 @@
         <v>16</v>
       </c>
       <c r="C859" t="n">
-        <v>-0.180902098242296</v>
+        <v>-0.248180751945395</v>
       </c>
     </row>
     <row r="860">
@@ -10472,7 +10466,7 @@
         <v>16</v>
       </c>
       <c r="C861" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.390075121418388</v>
       </c>
     </row>
     <row r="862">
@@ -10505,7 +10499,7 @@
         <v>16</v>
       </c>
       <c r="C864" t="n">
-        <v>-0.0520691453626161</v>
+        <v>0.153123229706923</v>
       </c>
     </row>
     <row r="865">
@@ -10516,7 +10510,7 @@
         <v>16</v>
       </c>
       <c r="C865" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.248156341555348</v>
       </c>
     </row>
     <row r="866">
@@ -10549,7 +10543,7 @@
         <v>16</v>
       </c>
       <c r="C868" t="n">
-        <v>-0.163604032426159</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="869">
@@ -10560,7 +10554,7 @@
         <v>16</v>
       </c>
       <c r="C869" t="n">
-        <v>-0.161888986248506</v>
+        <v>-0.181812154867327</v>
       </c>
     </row>
     <row r="870">
@@ -10571,7 +10565,7 @@
         <v>16</v>
       </c>
       <c r="C870" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.301230803910506</v>
       </c>
     </row>
     <row r="871">
@@ -10604,7 +10598,7 @@
         <v>16</v>
       </c>
       <c r="C873" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.207249710126163</v>
       </c>
     </row>
     <row r="874">
@@ -10615,7 +10609,7 @@
         <v>16</v>
       </c>
       <c r="C874" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.215125647718307</v>
       </c>
     </row>
     <row r="875">
@@ -10626,7 +10620,7 @@
         <v>16</v>
       </c>
       <c r="C875" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.17546872185829</v>
       </c>
     </row>
     <row r="876">
@@ -10637,7 +10631,7 @@
         <v>16</v>
       </c>
       <c r="C876" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.293734379006365</v>
       </c>
     </row>
     <row r="877">
@@ -10659,7 +10653,7 @@
         <v>16</v>
       </c>
       <c r="C878" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.255855504044469</v>
       </c>
     </row>
     <row r="879">
@@ -10681,7 +10675,7 @@
         <v>16</v>
       </c>
       <c r="C880" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.24841839410944</v>
       </c>
     </row>
     <row r="881">
@@ -10725,7 +10719,7 @@
         <v>16</v>
       </c>
       <c r="C884" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.23104630199756</v>
       </c>
     </row>
     <row r="885">
@@ -10747,7 +10741,7 @@
         <v>16</v>
       </c>
       <c r="C886" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.265393845018141</v>
       </c>
     </row>
     <row r="887">
@@ -10758,7 +10752,7 @@
         <v>16</v>
       </c>
       <c r="C887" t="n">
-        <v>-0.0597885793013448</v>
+        <v>0.263382111882275</v>
       </c>
     </row>
     <row r="888">
@@ -10769,7 +10763,7 @@
         <v>16</v>
       </c>
       <c r="C888" t="n">
-        <v>-0.164370615553423</v>
+        <v>-0.261770078391243</v>
       </c>
     </row>
     <row r="889">
@@ -10780,7 +10774,7 @@
         <v>16</v>
       </c>
       <c r="C889" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.165218933539368</v>
       </c>
     </row>
     <row r="890">
@@ -10813,7 +10807,7 @@
         <v>16</v>
       </c>
       <c r="C892" t="n">
-        <v>-0.0741360241676272</v>
+        <v>0.562574598083293</v>
       </c>
     </row>
     <row r="893">
@@ -10824,7 +10818,7 @@
         <v>16</v>
       </c>
       <c r="C893" t="n">
-        <v>-0.189132149491051</v>
+        <v>-0.311616505665287</v>
       </c>
     </row>
     <row r="894">
@@ -10835,7 +10829,7 @@
         <v>16</v>
       </c>
       <c r="C894" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.509805350736121</v>
       </c>
     </row>
     <row r="895">
@@ -10868,7 +10862,7 @@
         <v>16</v>
       </c>
       <c r="C897" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.316486342451578</v>
       </c>
     </row>
     <row r="898">
@@ -10879,7 +10873,7 @@
         <v>16</v>
       </c>
       <c r="C898" t="n">
-        <v>-0.158763009891615</v>
+        <v>-0.17872927024431</v>
       </c>
     </row>
     <row r="899">
@@ -10923,7 +10917,7 @@
         <v>16</v>
       </c>
       <c r="C902" t="n">
-        <v>-0.186637224034331</v>
+        <v>0.0128690546161927</v>
       </c>
     </row>
     <row r="903">
@@ -10945,7 +10939,7 @@
         <v>16</v>
       </c>
       <c r="C904" t="n">
-        <v>-0.198269319312699</v>
+        <v>-0.226502913264661</v>
       </c>
     </row>
     <row r="905">
@@ -10956,7 +10950,7 @@
         <v>16</v>
       </c>
       <c r="C905" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.179152369979183</v>
       </c>
     </row>
     <row r="906">
@@ -10967,7 +10961,7 @@
         <v>16</v>
       </c>
       <c r="C906" t="n">
-        <v>-0.169638090519553</v>
+        <v>-0.203729596736631</v>
       </c>
     </row>
     <row r="907">
@@ -11011,7 +11005,7 @@
         <v>16</v>
       </c>
       <c r="C910" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.565938558297868</v>
       </c>
     </row>
     <row r="911">
@@ -11022,7 +11016,7 @@
         <v>16</v>
       </c>
       <c r="C911" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.17791929739275</v>
       </c>
     </row>
     <row r="912">
@@ -11033,7 +11027,7 @@
         <v>16</v>
       </c>
       <c r="C912" t="n">
-        <v>-0.181280672517037</v>
+        <v>-0.164134749555802</v>
       </c>
     </row>
     <row r="913">
@@ -11044,7 +11038,7 @@
         <v>16</v>
       </c>
       <c r="C913" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.189638265520234</v>
       </c>
     </row>
     <row r="914">
@@ -11055,7 +11049,7 @@
         <v>16</v>
       </c>
       <c r="C914" t="n">
-        <v>-0.17047197900359</v>
+        <v>-0.220663319363384</v>
       </c>
     </row>
     <row r="915">
@@ -11066,7 +11060,7 @@
         <v>16</v>
       </c>
       <c r="C915" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.170898738914981</v>
       </c>
     </row>
     <row r="916">
@@ -11077,7 +11071,7 @@
         <v>16</v>
       </c>
       <c r="C916" t="n">
-        <v>-0.188348565024568</v>
+        <v>-0.333633985548909</v>
       </c>
     </row>
     <row r="917">
@@ -11132,7 +11126,7 @@
         <v>16</v>
       </c>
       <c r="C921" t="n">
-        <v>-0.162170013260668</v>
+        <v>0.188459108276247</v>
       </c>
     </row>
     <row r="922">
@@ -11143,7 +11137,7 @@
         <v>16</v>
       </c>
       <c r="C922" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.53267545475767</v>
       </c>
     </row>
     <row r="923">
@@ -11154,7 +11148,7 @@
         <v>16</v>
       </c>
       <c r="C923" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.16374059064031</v>
       </c>
     </row>
     <row r="924">
@@ -11187,7 +11181,7 @@
         <v>16</v>
       </c>
       <c r="C926" t="n">
-        <v>-0.19842740485375</v>
+        <v>-0.296837326236474</v>
       </c>
     </row>
     <row r="927">
@@ -11209,7 +11203,7 @@
         <v>16</v>
       </c>
       <c r="C928" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.182734518352943</v>
       </c>
     </row>
     <row r="929">
@@ -11220,7 +11214,7 @@
         <v>16</v>
       </c>
       <c r="C929" t="n">
-        <v>-0.212210965408145</v>
+        <v>-0.391074504120753</v>
       </c>
     </row>
     <row r="930">
@@ -11231,7 +11225,7 @@
         <v>16</v>
       </c>
       <c r="C930" t="n">
-        <v>-0.168598056301957</v>
+        <v>-0.167919830613901</v>
       </c>
     </row>
     <row r="931">
@@ -11242,7 +11236,7 @@
         <v>16</v>
       </c>
       <c r="C931" t="n">
-        <v>-0.179289719497412</v>
+        <v>-0.310052482881029</v>
       </c>
     </row>
     <row r="932">
@@ -11264,7 +11258,7 @@
         <v>16</v>
       </c>
       <c r="C933" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.165713726596709</v>
       </c>
     </row>
     <row r="934">
@@ -11275,7 +11269,7 @@
         <v>16</v>
       </c>
       <c r="C934" t="n">
-        <v>-0.168785859645574</v>
+        <v>-0.296143515438758</v>
       </c>
     </row>
     <row r="935">
@@ -11286,7 +11280,7 @@
         <v>16</v>
       </c>
       <c r="C935" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.233989012624567</v>
       </c>
     </row>
     <row r="936">
@@ -11297,7 +11291,7 @@
         <v>16</v>
       </c>
       <c r="C936" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.270778200623804</v>
       </c>
     </row>
     <row r="937">
@@ -11308,7 +11302,7 @@
         <v>16</v>
       </c>
       <c r="C937" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.162420852764134</v>
       </c>
     </row>
     <row r="938">
@@ -11319,7 +11313,7 @@
         <v>16</v>
       </c>
       <c r="C938" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.323368327538704</v>
       </c>
     </row>
     <row r="939">
@@ -11330,7 +11324,7 @@
         <v>16</v>
       </c>
       <c r="C939" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.184503826344079</v>
       </c>
     </row>
     <row r="940">
@@ -11341,7 +11335,7 @@
         <v>16</v>
       </c>
       <c r="C940" t="n">
-        <v>-0.149829256894056</v>
+        <v>-0.00197206506561098</v>
       </c>
     </row>
     <row r="941">
@@ -11363,7 +11357,7 @@
         <v>16</v>
       </c>
       <c r="C942" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.171679169885491</v>
       </c>
     </row>
     <row r="943">
@@ -11374,7 +11368,7 @@
         <v>16</v>
       </c>
       <c r="C943" t="n">
-        <v>-0.170145807724119</v>
+        <v>-0.226780565062215</v>
       </c>
     </row>
     <row r="944">
@@ -11407,7 +11401,7 @@
         <v>16</v>
       </c>
       <c r="C946" t="n">
-        <v>-0.159763313609468</v>
+        <v>0.0817449983547988</v>
       </c>
     </row>
     <row r="947">
@@ -11429,7 +11423,7 @@
         <v>16</v>
       </c>
       <c r="C948" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.562966863102174</v>
       </c>
     </row>
     <row r="949">
@@ -11440,7 +11434,7 @@
         <v>16</v>
       </c>
       <c r="C949" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.240923332604149</v>
       </c>
     </row>
     <row r="950">
@@ -11462,7 +11456,7 @@
         <v>16</v>
       </c>
       <c r="C951" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.75338794255554</v>
       </c>
     </row>
     <row r="952">
@@ -11495,7 +11489,7 @@
         <v>16</v>
       </c>
       <c r="C954" t="n">
-        <v>-0.16446605551948</v>
+        <v>-0.178810862087013</v>
       </c>
     </row>
     <row r="955">
@@ -11528,7 +11522,7 @@
         <v>16</v>
       </c>
       <c r="C957" t="n">
-        <v>-0.0686926036290598</v>
+        <v>0.155752442397496</v>
       </c>
     </row>
     <row r="958">
@@ -11550,7 +11544,7 @@
         <v>16</v>
       </c>
       <c r="C959" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.18076211689597</v>
       </c>
     </row>
     <row r="960">
@@ -11561,7 +11555,7 @@
         <v>16</v>
       </c>
       <c r="C960" t="n">
-        <v>-0.162425429558428</v>
+        <v>-0.119810920441767</v>
       </c>
     </row>
     <row r="961">
@@ -11572,7 +11566,7 @@
         <v>16</v>
       </c>
       <c r="C961" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.182659823418837</v>
       </c>
     </row>
     <row r="962">
@@ -11583,7 +11577,7 @@
         <v>16</v>
       </c>
       <c r="C962" t="n">
-        <v>-0.160229970632778</v>
+        <v>0.0620820085227974</v>
       </c>
     </row>
     <row r="963">
@@ -11616,7 +11610,7 @@
         <v>16</v>
       </c>
       <c r="C965" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.424880311756994</v>
       </c>
     </row>
     <row r="966">
@@ -11638,7 +11632,7 @@
         <v>16</v>
       </c>
       <c r="C967" t="n">
-        <v>-0.168838700216953</v>
+        <v>-0.515351070315943</v>
       </c>
     </row>
     <row r="968">
@@ -11704,7 +11698,7 @@
         <v>16</v>
       </c>
       <c r="C973" t="n">
-        <v>-0.165128179004199</v>
+        <v>-0.283782287339111</v>
       </c>
     </row>
     <row r="974">
@@ -11715,7 +11709,7 @@
         <v>16</v>
       </c>
       <c r="C974" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.209145056823551</v>
       </c>
     </row>
     <row r="975">
@@ -11726,7 +11720,7 @@
         <v>16</v>
       </c>
       <c r="C975" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.0719604935045421</v>
       </c>
     </row>
     <row r="976">
@@ -11748,7 +11742,7 @@
         <v>16</v>
       </c>
       <c r="C977" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.176268641013971</v>
       </c>
     </row>
     <row r="978">
@@ -11770,7 +11764,7 @@
         <v>16</v>
       </c>
       <c r="C979" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.331600241083939</v>
       </c>
     </row>
     <row r="980">
@@ -11781,7 +11775,7 @@
         <v>16</v>
       </c>
       <c r="C980" t="n">
-        <v>-0.159763313609468</v>
+        <v>0.160844409078177</v>
       </c>
     </row>
     <row r="981">
@@ -11792,7 +11786,7 @@
         <v>16</v>
       </c>
       <c r="C981" t="n">
-        <v>-0.171331778743078</v>
+        <v>-0.2950704071832</v>
       </c>
     </row>
     <row r="982">
@@ -11814,7 +11808,7 @@
         <v>16</v>
       </c>
       <c r="C983" t="n">
-        <v>-0.159763313609468</v>
+        <v>0.0334412235567122</v>
       </c>
     </row>
     <row r="984">
@@ -11836,7 +11830,7 @@
         <v>16</v>
       </c>
       <c r="C985" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.443548313269069</v>
       </c>
     </row>
     <row r="986">
@@ -11847,7 +11841,7 @@
         <v>16</v>
       </c>
       <c r="C986" t="n">
-        <v>-0.16611983539322</v>
+        <v>-0.020039629190133</v>
       </c>
     </row>
     <row r="987">
@@ -11880,7 +11874,7 @@
         <v>16</v>
       </c>
       <c r="C989" t="n">
-        <v>-0.159763313609468</v>
+        <v>0.184338369717185</v>
       </c>
     </row>
     <row r="990">
@@ -11957,7 +11951,7 @@
         <v>16</v>
       </c>
       <c r="C996" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.162619504501648</v>
       </c>
     </row>
     <row r="997">
@@ -11968,7 +11962,7 @@
         <v>16</v>
       </c>
       <c r="C997" t="n">
-        <v>-0.156374149638618</v>
+        <v>-0.159433963919613</v>
       </c>
     </row>
     <row r="998">
@@ -11979,7 +11973,7 @@
         <v>16</v>
       </c>
       <c r="C998" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.00978707740327944</v>
       </c>
     </row>
     <row r="999">
@@ -11990,7 +11984,7 @@
         <v>16</v>
       </c>
       <c r="C999" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.195146872898426</v>
       </c>
     </row>
     <row r="1000">
@@ -12001,7 +11995,7 @@
         <v>16</v>
       </c>
       <c r="C1000" t="n">
-        <v>-0.159763313609468</v>
+        <v>0.279609489542096</v>
       </c>
     </row>
     <row r="1001">
@@ -12012,7 +12006,7 @@
         <v>16</v>
       </c>
       <c r="C1001" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.21460240096403</v>
       </c>
     </row>
     <row r="1002">
@@ -12034,7 +12028,7 @@
         <v>16</v>
       </c>
       <c r="C1003" t="n">
-        <v>-0.159431594429317</v>
+        <v>0.403977686383989</v>
       </c>
     </row>
     <row r="1004">
@@ -12078,7 +12072,7 @@
         <v>16</v>
       </c>
       <c r="C1007" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.281975405070259</v>
       </c>
     </row>
     <row r="1008">
@@ -12133,7 +12127,7 @@
         <v>16</v>
       </c>
       <c r="C1012" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.213144066799254</v>
       </c>
     </row>
     <row r="1013">
@@ -12144,7 +12138,7 @@
         <v>16</v>
       </c>
       <c r="C1013" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.181270483157428</v>
       </c>
     </row>
     <row r="1014">
@@ -12166,7 +12160,7 @@
         <v>16</v>
       </c>
       <c r="C1015" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.191954961560178</v>
       </c>
     </row>
     <row r="1016">
@@ -12177,7 +12171,7 @@
         <v>16</v>
       </c>
       <c r="C1016" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.133742360177033</v>
       </c>
     </row>
     <row r="1017">
@@ -12188,7 +12182,7 @@
         <v>16</v>
       </c>
       <c r="C1017" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.277051956788286</v>
       </c>
     </row>
     <row r="1018">
@@ -12199,7 +12193,7 @@
         <v>16</v>
       </c>
       <c r="C1018" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.388703032947217</v>
       </c>
     </row>
     <row r="1019">
@@ -12243,7 +12237,7 @@
         <v>16</v>
       </c>
       <c r="C1022" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.154655390137623</v>
       </c>
     </row>
     <row r="1023">
@@ -12254,7 +12248,7 @@
         <v>16</v>
       </c>
       <c r="C1023" t="n">
-        <v>-0.1740049545649</v>
+        <v>-0.182382061373856</v>
       </c>
     </row>
     <row r="1024">
@@ -12265,7 +12259,7 @@
         <v>16</v>
       </c>
       <c r="C1024" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.29679398944784</v>
       </c>
     </row>
     <row r="1025">
@@ -12276,7 +12270,7 @@
         <v>16</v>
       </c>
       <c r="C1025" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.173876215386806</v>
       </c>
     </row>
     <row r="1026">
@@ -12342,7 +12336,7 @@
         <v>16</v>
       </c>
       <c r="C1031" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.186380283031321</v>
       </c>
     </row>
     <row r="1032">
@@ -12353,7 +12347,7 @@
         <v>16</v>
       </c>
       <c r="C1032" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.182321534313329</v>
       </c>
     </row>
     <row r="1033">
@@ -12375,7 +12369,7 @@
         <v>16</v>
       </c>
       <c r="C1034" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.301593624580039</v>
       </c>
     </row>
     <row r="1035">
@@ -12463,7 +12457,7 @@
         <v>16</v>
       </c>
       <c r="C1042" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.59549552872734</v>
       </c>
     </row>
     <row r="1043">
@@ -12507,7 +12501,7 @@
         <v>16</v>
       </c>
       <c r="C1046" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.25269730330525</v>
       </c>
     </row>
     <row r="1047">
@@ -12639,7 +12633,7 @@
         <v>16</v>
       </c>
       <c r="C1058" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.459803105094732</v>
       </c>
     </row>
     <row r="1059">
@@ -12650,7 +12644,7 @@
         <v>16</v>
       </c>
       <c r="C1059" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.150615102879959</v>
       </c>
     </row>
     <row r="1060">
@@ -12661,7 +12655,7 @@
         <v>16</v>
       </c>
       <c r="C1060" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.0124732770064573</v>
       </c>
     </row>
     <row r="1061">
@@ -12672,7 +12666,7 @@
         <v>16</v>
       </c>
       <c r="C1061" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.232941130845165</v>
       </c>
     </row>
     <row r="1062">
@@ -12683,7 +12677,7 @@
         <v>16</v>
       </c>
       <c r="C1062" t="n">
-        <v>-0.184057375002462</v>
+        <v>-0.511731413291044</v>
       </c>
     </row>
     <row r="1063">
@@ -12694,7 +12688,7 @@
         <v>16</v>
       </c>
       <c r="C1063" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.212490359039266</v>
       </c>
     </row>
     <row r="1064">
@@ -12705,7 +12699,7 @@
         <v>16</v>
       </c>
       <c r="C1064" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.183610988266298</v>
       </c>
     </row>
     <row r="1065">
@@ -12749,7 +12743,7 @@
         <v>16</v>
       </c>
       <c r="C1068" t="n">
-        <v>-0.173611111111111</v>
+        <v>0.190113635436411</v>
       </c>
     </row>
     <row r="1069">
@@ -12760,7 +12754,7 @@
         <v>16</v>
       </c>
       <c r="C1069" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.189260210086106</v>
       </c>
     </row>
     <row r="1070">
@@ -12793,7 +12787,7 @@
         <v>16</v>
       </c>
       <c r="C1072" t="n">
-        <v>-0.175844047443666</v>
+        <v>-0.154365014203818</v>
       </c>
     </row>
     <row r="1073">
@@ -12804,7 +12798,7 @@
         <v>16</v>
       </c>
       <c r="C1073" t="n">
-        <v>-0.175463142267423</v>
+        <v>-0.214143299571628</v>
       </c>
     </row>
     <row r="1074">
@@ -12826,7 +12820,7 @@
         <v>16</v>
       </c>
       <c r="C1075" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.272707917147448</v>
       </c>
     </row>
     <row r="1076">
@@ -12837,7 +12831,7 @@
         <v>16</v>
       </c>
       <c r="C1076" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.242528208428696</v>
       </c>
     </row>
     <row r="1077">
@@ -12859,7 +12853,7 @@
         <v>16</v>
       </c>
       <c r="C1078" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.336258706731211</v>
       </c>
     </row>
     <row r="1079">
@@ -12870,7 +12864,7 @@
         <v>16</v>
       </c>
       <c r="C1079" t="n">
-        <v>-0.174271735257642</v>
+        <v>-0.576838901057183</v>
       </c>
     </row>
     <row r="1080">
@@ -12892,7 +12886,7 @@
         <v>16</v>
       </c>
       <c r="C1081" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.261084285949968</v>
       </c>
     </row>
     <row r="1082">
@@ -12903,7 +12897,7 @@
         <v>16</v>
       </c>
       <c r="C1082" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.259669524872175</v>
       </c>
     </row>
     <row r="1083">
@@ -12925,7 +12919,7 @@
         <v>16</v>
       </c>
       <c r="C1084" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.438375292241339</v>
       </c>
     </row>
     <row r="1085">
@@ -12936,7 +12930,7 @@
         <v>16</v>
       </c>
       <c r="C1085" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.146101453752422</v>
       </c>
     </row>
     <row r="1086">
@@ -12958,7 +12952,7 @@
         <v>16</v>
       </c>
       <c r="C1087" t="n">
-        <v>-0.173611111111111</v>
+        <v>-1.15323537153019</v>
       </c>
     </row>
     <row r="1088">
@@ -12980,7 +12974,7 @@
         <v>16</v>
       </c>
       <c r="C1089" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.295466329441782</v>
       </c>
     </row>
     <row r="1090">
@@ -13002,7 +12996,7 @@
         <v>16</v>
       </c>
       <c r="C1091" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.295348720136604</v>
       </c>
     </row>
     <row r="1092">
@@ -13013,7 +13007,7 @@
         <v>16</v>
       </c>
       <c r="C1092" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.369816729065118</v>
       </c>
     </row>
     <row r="1093">
@@ -13024,7 +13018,7 @@
         <v>16</v>
       </c>
       <c r="C1093" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.226790491601731</v>
       </c>
     </row>
     <row r="1094">
@@ -13057,7 +13051,7 @@
         <v>16</v>
       </c>
       <c r="C1096" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.847995824164838</v>
       </c>
     </row>
     <row r="1097">
@@ -13112,7 +13106,7 @@
         <v>16</v>
       </c>
       <c r="C1101" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.300343493698513</v>
       </c>
     </row>
     <row r="1102">
@@ -13123,7 +13117,7 @@
         <v>16</v>
       </c>
       <c r="C1102" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.477483805045439</v>
       </c>
     </row>
     <row r="1103">
@@ -13178,7 +13172,7 @@
         <v>16</v>
       </c>
       <c r="C1107" t="n">
-        <v>-0.173611111111111</v>
+        <v>0.00094852821584468</v>
       </c>
     </row>
     <row r="1108">
@@ -13189,7 +13183,7 @@
         <v>16</v>
       </c>
       <c r="C1108" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.235472271132771</v>
       </c>
     </row>
     <row r="1109">
@@ -13200,7 +13194,7 @@
         <v>16</v>
       </c>
       <c r="C1109" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.200281748493093</v>
       </c>
     </row>
     <row r="1110">
@@ -13211,7 +13205,7 @@
         <v>16</v>
       </c>
       <c r="C1110" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.190656195179133</v>
       </c>
     </row>
     <row r="1111">
@@ -13222,7 +13216,7 @@
         <v>16</v>
       </c>
       <c r="C1111" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.21468290795183</v>
       </c>
     </row>
     <row r="1112">
@@ -13244,7 +13238,7 @@
         <v>16</v>
       </c>
       <c r="C1113" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.280122390870028</v>
       </c>
     </row>
     <row r="1114">
@@ -13255,7 +13249,7 @@
         <v>16</v>
       </c>
       <c r="C1114" t="n">
-        <v>-0.176586330094921</v>
+        <v>-0.191015208609282</v>
       </c>
     </row>
     <row r="1115">
@@ -13266,7 +13260,7 @@
         <v>16</v>
       </c>
       <c r="C1115" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.186789434780016</v>
       </c>
     </row>
     <row r="1116">
@@ -13277,7 +13271,7 @@
         <v>16</v>
       </c>
       <c r="C1116" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.258848843345961</v>
       </c>
     </row>
     <row r="1117">
@@ -13288,7 +13282,7 @@
         <v>16</v>
       </c>
       <c r="C1117" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.318542571924749</v>
       </c>
     </row>
     <row r="1118">
@@ -13332,7 +13326,7 @@
         <v>16</v>
       </c>
       <c r="C1121" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.638060647724447</v>
       </c>
     </row>
     <row r="1122">
@@ -13343,7 +13337,7 @@
         <v>16</v>
       </c>
       <c r="C1122" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.403363143034078</v>
       </c>
     </row>
     <row r="1123">
@@ -13365,7 +13359,7 @@
         <v>16</v>
       </c>
       <c r="C1124" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.277043041917526</v>
       </c>
     </row>
     <row r="1125">
@@ -13376,7 +13370,7 @@
         <v>16</v>
       </c>
       <c r="C1125" t="n">
-        <v>-0.176881356936714</v>
+        <v>0.21915804624579</v>
       </c>
     </row>
     <row r="1126">
@@ -13409,7 +13403,7 @@
         <v>16</v>
       </c>
       <c r="C1128" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.172162673923835</v>
       </c>
     </row>
     <row r="1129">
@@ -13420,7 +13414,7 @@
         <v>16</v>
       </c>
       <c r="C1129" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.314544491916136</v>
       </c>
     </row>
     <row r="1130">
@@ -13431,7 +13425,7 @@
         <v>16</v>
       </c>
       <c r="C1130" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.26891605181174</v>
       </c>
     </row>
     <row r="1131">
@@ -13442,7 +13436,7 @@
         <v>16</v>
       </c>
       <c r="C1131" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.208020477843245</v>
       </c>
     </row>
     <row r="1132">
@@ -13464,7 +13458,7 @@
         <v>16</v>
       </c>
       <c r="C1133" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.151600546208376</v>
       </c>
     </row>
     <row r="1134">
@@ -13486,7 +13480,7 @@
         <v>16</v>
       </c>
       <c r="C1135" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.189639721627325</v>
       </c>
     </row>
     <row r="1136">
@@ -13497,7 +13491,7 @@
         <v>16</v>
       </c>
       <c r="C1136" t="n">
-        <v>-0.181405885653257</v>
+        <v>-0.453610240594318</v>
       </c>
     </row>
     <row r="1137">
@@ -13508,7 +13502,7 @@
         <v>16</v>
       </c>
       <c r="C1137" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.361831445393304</v>
       </c>
     </row>
     <row r="1138">
@@ -13541,7 +13535,7 @@
         <v>16</v>
       </c>
       <c r="C1140" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.357424894615372</v>
       </c>
     </row>
     <row r="1141">
@@ -13574,7 +13568,7 @@
         <v>16</v>
       </c>
       <c r="C1143" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.641614944643061</v>
       </c>
     </row>
     <row r="1144">
@@ -13618,7 +13612,7 @@
         <v>16</v>
       </c>
       <c r="C1147" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.321356381623104</v>
       </c>
     </row>
     <row r="1148">
@@ -13629,7 +13623,7 @@
         <v>16</v>
       </c>
       <c r="C1148" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.87250649284071</v>
       </c>
     </row>
     <row r="1149">
@@ -13640,7 +13634,7 @@
         <v>16</v>
       </c>
       <c r="C1149" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.20920342366005</v>
       </c>
     </row>
     <row r="1150">
@@ -13651,7 +13645,7 @@
         <v>16</v>
       </c>
       <c r="C1150" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.285109208199795</v>
       </c>
     </row>
     <row r="1151">
@@ -13673,7 +13667,7 @@
         <v>16</v>
       </c>
       <c r="C1152" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.336152955116854</v>
       </c>
     </row>
     <row r="1153">
@@ -13684,7 +13678,7 @@
         <v>16</v>
       </c>
       <c r="C1153" t="n">
-        <v>-0.162877216131955</v>
+        <v>-0.079342443628232</v>
       </c>
     </row>
     <row r="1154">
@@ -13717,7 +13711,7 @@
         <v>16</v>
       </c>
       <c r="C1156" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.74203457560469</v>
       </c>
     </row>
     <row r="1157">
@@ -13739,7 +13733,7 @@
         <v>16</v>
       </c>
       <c r="C1158" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.199908746057718</v>
       </c>
     </row>
     <row r="1159">
@@ -13772,7 +13766,7 @@
         <v>16</v>
       </c>
       <c r="C1161" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.214335492195835</v>
       </c>
     </row>
     <row r="1162">
@@ -13794,7 +13788,7 @@
         <v>16</v>
       </c>
       <c r="C1163" t="n">
-        <v>-0.16524018389155</v>
+        <v>0.0668328672259346</v>
       </c>
     </row>
     <row r="1164">
@@ -13816,7 +13810,7 @@
         <v>16</v>
       </c>
       <c r="C1165" t="n">
-        <v>-0.179747118279503</v>
+        <v>0.0548247875153048</v>
       </c>
     </row>
     <row r="1166">
@@ -13827,7 +13821,7 @@
         <v>16</v>
       </c>
       <c r="C1166" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.11550899943148</v>
       </c>
     </row>
     <row r="1167">
@@ -13849,7 +13843,7 @@
         <v>16</v>
       </c>
       <c r="C1168" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.356489032254282</v>
       </c>
     </row>
     <row r="1169">
@@ -13871,7 +13865,7 @@
         <v>16</v>
       </c>
       <c r="C1170" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.175114085499038</v>
       </c>
     </row>
     <row r="1171">
@@ -13915,7 +13909,7 @@
         <v>16</v>
       </c>
       <c r="C1174" t="n">
-        <v>-0.161307016039326</v>
+        <v>0.239929236539116</v>
       </c>
     </row>
     <row r="1175">
@@ -13959,7 +13953,7 @@
         <v>16</v>
       </c>
       <c r="C1178" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.194350358205622</v>
       </c>
     </row>
     <row r="1179">
@@ -13992,7 +13986,7 @@
         <v>16</v>
       </c>
       <c r="C1181" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.368418221545276</v>
       </c>
     </row>
     <row r="1182">
@@ -14036,7 +14030,7 @@
         <v>16</v>
       </c>
       <c r="C1185" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.212527914297039</v>
       </c>
     </row>
     <row r="1186">
@@ -14047,7 +14041,7 @@
         <v>16</v>
       </c>
       <c r="C1186" t="n">
-        <v>-0.194622525538841</v>
+        <v>-0.369448120796979</v>
       </c>
     </row>
     <row r="1187">
@@ -14069,7 +14063,7 @@
         <v>16</v>
       </c>
       <c r="C1188" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.259561728808225</v>
       </c>
     </row>
     <row r="1189">
@@ -14091,7 +14085,7 @@
         <v>16</v>
       </c>
       <c r="C1190" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.19601410149496</v>
       </c>
     </row>
     <row r="1191">
@@ -14113,7 +14107,7 @@
         <v>16</v>
       </c>
       <c r="C1192" t="n">
-        <v>-0.183268720874767</v>
+        <v>-0.279175615744511</v>
       </c>
     </row>
     <row r="1193">
@@ -14146,7 +14140,7 @@
         <v>16</v>
       </c>
       <c r="C1195" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.36966226341716</v>
       </c>
     </row>
     <row r="1196">
@@ -14157,7 +14151,7 @@
         <v>16</v>
       </c>
       <c r="C1196" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.291403443328038</v>
       </c>
     </row>
     <row r="1197">
@@ -14190,7 +14184,7 @@
         <v>16</v>
       </c>
       <c r="C1199" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.686224383493178</v>
       </c>
     </row>
     <row r="1200">
@@ -14201,7 +14195,7 @@
         <v>16</v>
       </c>
       <c r="C1200" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.18624434712443</v>
       </c>
     </row>
     <row r="1201">
@@ -14212,7 +14206,7 @@
         <v>16</v>
       </c>
       <c r="C1201" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.494944456104687</v>
       </c>
     </row>
   </sheetData>
@@ -14427,7 +14421,7 @@
         <v>-1.86</v>
       </c>
       <c r="E12" t="n">
-        <v>5.13538461538462</v>
+        <v>7.26496844036325</v>
       </c>
     </row>
     <row r="13">
@@ -14784,7 +14778,7 @@
         <v>739.459999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>-21.5415384615384</v>
+        <v>-1552.34583706448</v>
       </c>
     </row>
     <row r="34">
@@ -14971,7 +14965,7 @@
         <v>1.706</v>
       </c>
       <c r="E44" t="n">
-        <v>1.84861538461538</v>
+        <v>1.87469614394596</v>
       </c>
     </row>
     <row r="45">
@@ -14988,7 +14982,7 @@
         <v>4.218</v>
       </c>
       <c r="E45" t="n">
-        <v>1.65538461538462</v>
+        <v>1.82903406043126</v>
       </c>
     </row>
     <row r="46">
@@ -15005,7 +14999,7 @@
         <v>1.578</v>
       </c>
       <c r="E46" t="n">
-        <v>1.85846153846154</v>
+        <v>1.24888219174044</v>
       </c>
     </row>
     <row r="47">
@@ -15022,7 +15016,7 @@
         <v>3.683</v>
       </c>
       <c r="E47" t="n">
-        <v>1.69653846153846</v>
+        <v>1.58453313309452</v>
       </c>
     </row>
     <row r="48">
@@ -15056,7 +15050,7 @@
         <v>2.44</v>
       </c>
       <c r="E49" t="n">
-        <v>1.79215384615385</v>
+        <v>1.75909657359267</v>
       </c>
     </row>
     <row r="50">
@@ -15073,7 +15067,7 @@
         <v>0.579999999999998</v>
       </c>
       <c r="E50" t="n">
-        <v>1.93523076923077</v>
+        <v>1.77408136042712</v>
       </c>
     </row>
     <row r="51">
@@ -15090,7 +15084,7 @@
         <v>-1.918</v>
       </c>
       <c r="E51" t="n">
-        <v>2.12738461538462</v>
+        <v>1.90068669799598</v>
       </c>
     </row>
     <row r="52">
@@ -15107,7 +15101,7 @@
         <v>0.672000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>1.92815384615385</v>
+        <v>1.69243880330475</v>
       </c>
     </row>
     <row r="53">
@@ -15124,7 +15118,7 @@
         <v>0.352999999999998</v>
       </c>
       <c r="E53" t="n">
-        <v>1.95269230769231</v>
+        <v>1.87531462416869</v>
       </c>
     </row>
     <row r="54">
@@ -15158,7 +15152,7 @@
         <v>0.181000000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>1.96592307692308</v>
+        <v>2.08811014385877</v>
       </c>
     </row>
     <row r="56">
@@ -15175,7 +15169,7 @@
         <v>1.311</v>
       </c>
       <c r="E56" t="n">
-        <v>1.879</v>
+        <v>1.11964075839186</v>
       </c>
     </row>
     <row r="57">
@@ -15192,7 +15186,7 @@
         <v>2.862</v>
       </c>
       <c r="E57" t="n">
-        <v>1.75969230769231</v>
+        <v>1.73837192516443</v>
       </c>
     </row>
     <row r="58">
@@ -15498,7 +15492,7 @@
         <v>11</v>
       </c>
       <c r="E75" t="n">
-        <v>8.75</v>
+        <v>23.5955572767653</v>
       </c>
     </row>
     <row r="76">
@@ -15871,13 +15865,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
         <v>14</v>
@@ -15888,13 +15882,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
         <v>14</v>
@@ -15911,7 +15905,7 @@
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>14</v>
@@ -15928,7 +15922,7 @@
         <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
         <v>14</v>
@@ -15945,7 +15939,7 @@
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D17" t="n">
         <v>14</v>
@@ -15962,7 +15956,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -15979,7 +15973,7 @@
         <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D19" t="n">
         <v>14</v>
@@ -15996,7 +15990,7 @@
         <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D20" t="n">
         <v>14</v>
@@ -16013,7 +16007,7 @@
         <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D21" t="n">
         <v>14</v>
@@ -16030,7 +16024,7 @@
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D22" t="n">
         <v>14</v>
@@ -16047,7 +16041,7 @@
         <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D23" t="n">
         <v>14</v>
@@ -16058,13 +16052,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B24" t="s">
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D24" t="n">
         <v>14</v>
@@ -16075,13 +16069,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B25" t="s">
         <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D25" t="n">
         <v>14</v>
@@ -16092,13 +16086,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
         <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D26" t="n">
         <v>14</v>
@@ -16109,13 +16103,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D27" t="n">
         <v>14</v>
@@ -16132,7 +16126,7 @@
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D28" t="n">
         <v>14</v>
@@ -16149,7 +16143,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D29" t="n">
         <v>14</v>
@@ -16166,7 +16160,7 @@
         <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D30" t="n">
         <v>14</v>
@@ -16183,7 +16177,7 @@
         <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D31" t="n">
         <v>14</v>
@@ -16200,7 +16194,7 @@
         <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D32" t="n">
         <v>14</v>
@@ -16217,7 +16211,7 @@
         <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D33" t="n">
         <v>14</v>
@@ -16234,7 +16228,7 @@
         <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D34" t="n">
         <v>14</v>
@@ -16245,13 +16239,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B35" t="s">
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D35" t="n">
         <v>14</v>
@@ -16262,13 +16256,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B36" t="s">
         <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D36" t="n">
         <v>14</v>
@@ -16279,13 +16273,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B37" t="s">
         <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D37" t="n">
         <v>14</v>
@@ -16296,13 +16290,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B38" t="s">
         <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D38" t="n">
         <v>14</v>
@@ -16313,13 +16307,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B39" t="s">
         <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D39" t="n">
         <v>14</v>
@@ -16330,13 +16324,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B40" t="s">
         <v>16</v>
       </c>
       <c r="C40" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D40" t="n">
         <v>14</v>
@@ -16353,7 +16347,7 @@
         <v>16</v>
       </c>
       <c r="C41" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D41" t="n">
         <v>14</v>
@@ -16370,7 +16364,7 @@
         <v>16</v>
       </c>
       <c r="C42" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D42" t="n">
         <v>14</v>
@@ -16387,7 +16381,7 @@
         <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D43" t="n">
         <v>14</v>
@@ -16404,7 +16398,7 @@
         <v>16</v>
       </c>
       <c r="C44" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D44" t="n">
         <v>14</v>
@@ -16421,7 +16415,7 @@
         <v>16</v>
       </c>
       <c r="C45" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D45" t="n">
         <v>14</v>
@@ -16432,13 +16426,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B46" t="s">
         <v>16</v>
       </c>
       <c r="C46" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D46" t="n">
         <v>14</v>
@@ -16449,13 +16443,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B47" t="s">
         <v>16</v>
       </c>
       <c r="C47" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D47" t="n">
         <v>14</v>
@@ -16466,13 +16460,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B48" t="s">
         <v>16</v>
       </c>
       <c r="C48" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D48" t="n">
         <v>14</v>
@@ -16483,13 +16477,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B49" t="s">
         <v>16</v>
       </c>
       <c r="C49" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D49" t="n">
         <v>14</v>
@@ -16500,13 +16494,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B50" t="s">
         <v>16</v>
       </c>
       <c r="C50" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D50" t="n">
         <v>14</v>
@@ -16517,13 +16511,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B51" t="s">
         <v>16</v>
       </c>
       <c r="C51" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D51" t="n">
         <v>14</v>
@@ -16534,13 +16528,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B52" t="s">
         <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D52" t="n">
         <v>14</v>
@@ -16551,13 +16545,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B53" t="s">
         <v>16</v>
       </c>
       <c r="C53" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D53" t="n">
         <v>14</v>
@@ -16574,7 +16568,7 @@
         <v>16</v>
       </c>
       <c r="C54" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D54" t="n">
         <v>14</v>
@@ -16591,7 +16585,7 @@
         <v>16</v>
       </c>
       <c r="C55" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D55" t="n">
         <v>14</v>
@@ -16608,7 +16602,7 @@
         <v>16</v>
       </c>
       <c r="C56" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D56" t="n">
         <v>14</v>
@@ -16619,16 +16613,16 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B57" t="s">
         <v>16</v>
       </c>
       <c r="C57" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D57" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E57" t="n">
         <v>1</v>
@@ -16636,16 +16630,16 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B58" t="s">
         <v>16</v>
       </c>
       <c r="C58" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D58" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E58" t="n">
         <v>1</v>
@@ -16653,16 +16647,16 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B59" t="s">
         <v>16</v>
       </c>
       <c r="C59" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D59" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E59" t="n">
         <v>1</v>
@@ -16670,16 +16664,16 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B60" t="s">
         <v>16</v>
       </c>
       <c r="C60" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E60" t="n">
         <v>1</v>
@@ -16687,16 +16681,16 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B61" t="s">
         <v>16</v>
       </c>
       <c r="C61" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D61" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
@@ -16704,16 +16698,16 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B62" t="s">
         <v>16</v>
       </c>
       <c r="C62" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D62" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
@@ -16721,16 +16715,16 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B63" t="s">
         <v>16</v>
       </c>
       <c r="C63" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D63" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
@@ -16738,16 +16732,16 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B64" t="s">
         <v>16</v>
       </c>
       <c r="C64" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D64" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E64" t="n">
         <v>1</v>
@@ -16755,16 +16749,16 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B65" t="s">
         <v>16</v>
       </c>
       <c r="C65" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D65" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -16772,16 +16766,16 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B66" t="s">
         <v>16</v>
       </c>
       <c r="C66" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D66" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -16795,216 +16789,12 @@
         <v>16</v>
       </c>
       <c r="C67" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D67" t="n">
         <v>13</v>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>21</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="s">
-        <v>43</v>
-      </c>
-      <c r="D68" t="n">
-        <v>13</v>
-      </c>
-      <c r="E68" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>21</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="s">
-        <v>44</v>
-      </c>
-      <c r="D69" t="n">
-        <v>13</v>
-      </c>
-      <c r="E69" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>21</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="s">
-        <v>45</v>
-      </c>
-      <c r="D70" t="n">
-        <v>13</v>
-      </c>
-      <c r="E70" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>21</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="s">
-        <v>46</v>
-      </c>
-      <c r="D71" t="n">
-        <v>13</v>
-      </c>
-      <c r="E71" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>21</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="s">
-        <v>47</v>
-      </c>
-      <c r="D72" t="n">
-        <v>13</v>
-      </c>
-      <c r="E72" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>21</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="s">
-        <v>48</v>
-      </c>
-      <c r="D73" t="n">
-        <v>13</v>
-      </c>
-      <c r="E73" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>21</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="s">
-        <v>49</v>
-      </c>
-      <c r="D74" t="n">
-        <v>13</v>
-      </c>
-      <c r="E74" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>21</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="s">
-        <v>50</v>
-      </c>
-      <c r="D75" t="n">
-        <v>13</v>
-      </c>
-      <c r="E75" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>21</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="s">
-        <v>51</v>
-      </c>
-      <c r="D76" t="n">
-        <v>13</v>
-      </c>
-      <c r="E76" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>21</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="s">
-        <v>52</v>
-      </c>
-      <c r="D77" t="n">
-        <v>13</v>
-      </c>
-      <c r="E77" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>21</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="s">
-        <v>53</v>
-      </c>
-      <c r="D78" t="n">
-        <v>13</v>
-      </c>
-      <c r="E78" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>21</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="s">
-        <v>54</v>
-      </c>
-      <c r="D79" t="n">
-        <v>13</v>
-      </c>
-      <c r="E79" t="n">
         <v>1</v>
       </c>
     </row>
